--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="2026-06" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="VWAP_Mensuel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-05" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -50,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -132,6 +134,23 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_202606" displayName="Table_202606" ref="A1:H23" headerRowCount="1">
   <autoFilter ref="A1:H23"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_202605" displayName="Table_202605" ref="A1:H21" headerRowCount="1">
+  <autoFilter ref="A1:H21"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -481,7 +500,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B2" t="n">
@@ -507,7 +526,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46175</v>
       </c>
       <c r="B3" t="n">
@@ -533,7 +552,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="B4" t="n">
@@ -559,7 +578,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46177</v>
       </c>
       <c r="B5" t="n">
@@ -585,7 +604,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B6" t="n">
@@ -611,7 +630,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46181</v>
       </c>
       <c r="B7" t="n">
@@ -637,7 +656,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="B8" t="n">
@@ -663,7 +682,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46183</v>
       </c>
       <c r="B9" t="n">
@@ -689,7 +708,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46184</v>
       </c>
       <c r="B10" t="n">
@@ -715,7 +734,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B11" t="n">
@@ -741,7 +760,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46188</v>
       </c>
       <c r="B12" t="n">
@@ -767,7 +786,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46189</v>
       </c>
       <c r="B13" t="n">
@@ -793,7 +812,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="B14" t="n">
@@ -819,7 +838,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46191</v>
       </c>
       <c r="B15" t="n">
@@ -845,7 +864,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B16" t="n">
@@ -871,7 +890,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="B17" t="n">
@@ -897,7 +916,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46196</v>
       </c>
       <c r="B18" t="n">
@@ -923,7 +942,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46197</v>
       </c>
       <c r="B19" t="n">
@@ -949,7 +968,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46198</v>
       </c>
       <c r="B20" t="n">
@@ -975,7 +994,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B21" t="n">
@@ -1001,7 +1020,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46202</v>
       </c>
       <c r="B22" t="n">
@@ -1027,7 +1046,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B23" t="n">
@@ -1066,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1084,14 +1103,603 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B2" t="n">
+        <v>155.1610870361328</v>
+      </c>
+      <c r="C2" t="n">
+        <v>158</v>
+      </c>
+      <c r="D2" t="n">
+        <v>160.6999969482422</v>
+      </c>
+      <c r="E2" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>158.3000030517578</v>
+      </c>
+      <c r="G2" t="n">
+        <v>165375</v>
+      </c>
+      <c r="H2" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B3" t="n">
+        <v>155.9467163085938</v>
+      </c>
+      <c r="C3" t="n">
+        <v>158.8000030517578</v>
+      </c>
+      <c r="D3" t="n">
+        <v>160.1999969482422</v>
+      </c>
+      <c r="E3" t="n">
+        <v>155.3000030517578</v>
+      </c>
+      <c r="F3" t="n">
+        <v>158.3000030517578</v>
+      </c>
+      <c r="G3" t="n">
+        <v>200597</v>
+      </c>
+      <c r="H3" t="n">
+        <v>158.4384986069248</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B4" t="n">
+        <v>163.41015625</v>
+      </c>
+      <c r="C4" t="n">
+        <v>166.3999938964844</v>
+      </c>
+      <c r="D4" t="n">
+        <v>166.3999938964844</v>
+      </c>
+      <c r="E4" t="n">
+        <v>160.3999938964844</v>
+      </c>
+      <c r="F4" t="n">
+        <v>160.6000061035156</v>
+      </c>
+      <c r="G4" t="n">
+        <v>176050</v>
+      </c>
+      <c r="H4" t="n">
+        <v>161.02441070224</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B5" t="n">
+        <v>158.3035888671875</v>
+      </c>
+      <c r="C5" t="n">
+        <v>161.1999969482422</v>
+      </c>
+      <c r="D5" t="n">
+        <v>167.6000061035156</v>
+      </c>
+      <c r="E5" t="n">
+        <v>161.1999969482422</v>
+      </c>
+      <c r="F5" t="n">
+        <v>166.6999969482422</v>
+      </c>
+      <c r="G5" t="n">
+        <v>162765</v>
+      </c>
+      <c r="H5" t="n">
+        <v>161.0649609611559</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B6" t="n">
+        <v>159.8748474121094</v>
+      </c>
+      <c r="C6" t="n">
+        <v>162.8000030517578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>163.3000030517578</v>
+      </c>
+      <c r="E6" t="n">
+        <v>159.8000030517578</v>
+      </c>
+      <c r="F6" t="n">
+        <v>160.3999938964844</v>
+      </c>
+      <c r="G6" t="n">
+        <v>96491</v>
+      </c>
+      <c r="H6" t="n">
+        <v>161.2738971185997</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B7" t="n">
+        <v>163.802978515625</v>
+      </c>
+      <c r="C7" t="n">
+        <v>166.8000030517578</v>
+      </c>
+      <c r="D7" t="n">
+        <v>166.8000030517578</v>
+      </c>
+      <c r="E7" t="n">
+        <v>162.3999938964844</v>
+      </c>
+      <c r="F7" t="n">
+        <v>162.8999938964844</v>
+      </c>
+      <c r="G7" t="n">
+        <v>195302</v>
+      </c>
+      <c r="H7" t="n">
+        <v>162.3568603939591</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B8" t="n">
+        <v>159.5802459716797</v>
+      </c>
+      <c r="C8" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>166.3999938964844</v>
+      </c>
+      <c r="E8" t="n">
+        <v>161.3000030517578</v>
+      </c>
+      <c r="F8" t="n">
+        <v>165.3000030517578</v>
+      </c>
+      <c r="G8" t="n">
+        <v>118993</v>
+      </c>
+      <c r="H8" t="n">
+        <v>162.3721284321257</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B9" t="n">
+        <v>163.6065826416016</v>
+      </c>
+      <c r="C9" t="n">
+        <v>166.6000061035156</v>
+      </c>
+      <c r="D9" t="n">
+        <v>167.6999969482422</v>
+      </c>
+      <c r="E9" t="n">
+        <v>164.6999969482422</v>
+      </c>
+      <c r="F9" t="n">
+        <v>165.3999938964844</v>
+      </c>
+      <c r="G9" t="n">
+        <v>98127</v>
+      </c>
+      <c r="H9" t="n">
+        <v>162.7139500950246</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B10" t="n">
+        <v>164.8832092285156</v>
+      </c>
+      <c r="C10" t="n">
+        <v>167.8999938964844</v>
+      </c>
+      <c r="D10" t="n">
+        <v>169</v>
+      </c>
+      <c r="E10" t="n">
+        <v>165.8000030517578</v>
+      </c>
+      <c r="F10" t="n">
+        <v>168</v>
+      </c>
+      <c r="G10" t="n">
+        <v>70133</v>
+      </c>
+      <c r="H10" t="n">
+        <v>162.9972523702643</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B11" t="n">
+        <v>160.4640655517578</v>
+      </c>
+      <c r="C11" t="n">
+        <v>163.3999938964844</v>
+      </c>
+      <c r="D11" t="n">
+        <v>167.1000061035156</v>
+      </c>
+      <c r="E11" t="n">
+        <v>162.1999969482422</v>
+      </c>
+      <c r="F11" t="n">
+        <v>165.3999938964844</v>
+      </c>
+      <c r="G11" t="n">
+        <v>92390</v>
+      </c>
+      <c r="H11" t="n">
+        <v>163.0242896233893</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B12" t="n">
+        <v>157.0269470214844</v>
+      </c>
+      <c r="C12" t="n">
+        <v>159.8999938964844</v>
+      </c>
+      <c r="D12" t="n">
+        <v>163.3000030517578</v>
+      </c>
+      <c r="E12" t="n">
+        <v>159.1000061035156</v>
+      </c>
+      <c r="F12" t="n">
+        <v>161.6000061035156</v>
+      </c>
+      <c r="G12" t="n">
+        <v>124749</v>
+      </c>
+      <c r="H12" t="n">
+        <v>162.764622709126</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B13" t="n">
+        <v>151.5275726318359</v>
+      </c>
+      <c r="C13" t="n">
+        <v>154.3000030517578</v>
+      </c>
+      <c r="D13" t="n">
+        <v>160.1000061035156</v>
+      </c>
+      <c r="E13" t="n">
+        <v>153.3000030517578</v>
+      </c>
+      <c r="F13" t="n">
+        <v>158.6000061035156</v>
+      </c>
+      <c r="G13" t="n">
+        <v>135563</v>
+      </c>
+      <c r="H13" t="n">
+        <v>162.0634527160542</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B14" t="n">
+        <v>154.0808563232422</v>
+      </c>
+      <c r="C14" t="n">
+        <v>156.8999938964844</v>
+      </c>
+      <c r="D14" t="n">
+        <v>159</v>
+      </c>
+      <c r="E14" t="n">
+        <v>155</v>
+      </c>
+      <c r="F14" t="n">
+        <v>155</v>
+      </c>
+      <c r="G14" t="n">
+        <v>91945</v>
+      </c>
+      <c r="H14" t="n">
+        <v>161.788786985953</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B15" t="n">
+        <v>156.5359344482422</v>
+      </c>
+      <c r="C15" t="n">
+        <v>159.3999938964844</v>
+      </c>
+      <c r="D15" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>157.1000061035156</v>
+      </c>
+      <c r="F15" t="n">
+        <v>157.3999938964844</v>
+      </c>
+      <c r="G15" t="n">
+        <v>53036</v>
+      </c>
+      <c r="H15" t="n">
+        <v>161.7176722554128</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B16" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>161.3999938964844</v>
+      </c>
+      <c r="D16" t="n">
+        <v>162.8000030517578</v>
+      </c>
+      <c r="E16" t="n">
+        <v>160</v>
+      </c>
+      <c r="F16" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>72064</v>
+      </c>
+      <c r="H16" t="n">
+        <v>161.7053214676087</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B17" t="n">
+        <v>162</v>
+      </c>
+      <c r="C17" t="n">
+        <v>162</v>
+      </c>
+      <c r="D17" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>160.6999969482422</v>
+      </c>
+      <c r="F17" t="n">
+        <v>161.6000061035156</v>
+      </c>
+      <c r="G17" t="n">
+        <v>69509</v>
+      </c>
+      <c r="H17" t="n">
+        <v>161.7159724619766</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B18" t="n">
+        <v>161.6000061035156</v>
+      </c>
+      <c r="C18" t="n">
+        <v>161.6000061035156</v>
+      </c>
+      <c r="D18" t="n">
+        <v>164.1999969482422</v>
+      </c>
+      <c r="E18" t="n">
+        <v>160.6999969482422</v>
+      </c>
+      <c r="F18" t="n">
+        <v>161.8999938964844</v>
+      </c>
+      <c r="G18" t="n">
+        <v>107500</v>
+      </c>
+      <c r="H18" t="n">
+        <v>161.7098331676465</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B19" t="n">
+        <v>161</v>
+      </c>
+      <c r="C19" t="n">
+        <v>161</v>
+      </c>
+      <c r="D19" t="n">
+        <v>164.3000030517578</v>
+      </c>
+      <c r="E19" t="n">
+        <v>159.3999938964844</v>
+      </c>
+      <c r="F19" t="n">
+        <v>162.1999969482422</v>
+      </c>
+      <c r="G19" t="n">
+        <v>92700</v>
+      </c>
+      <c r="H19" t="n">
+        <v>161.6788427868548</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B20" t="n">
+        <v>162.6000061035156</v>
+      </c>
+      <c r="C20" t="n">
+        <v>162.6000061035156</v>
+      </c>
+      <c r="D20" t="n">
+        <v>162.6000061035156</v>
+      </c>
+      <c r="E20" t="n">
+        <v>158.3000030517578</v>
+      </c>
+      <c r="F20" t="n">
+        <v>161.1000061035156</v>
+      </c>
+      <c r="G20" t="n">
+        <v>110364</v>
+      </c>
+      <c r="H20" t="n">
+        <v>161.7243571385826</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B21" t="n">
+        <v>158.3999938964844</v>
+      </c>
+      <c r="C21" t="n">
+        <v>158.3999938964844</v>
+      </c>
+      <c r="D21" t="n">
+        <v>163</v>
+      </c>
+      <c r="E21" t="n">
+        <v>158</v>
+      </c>
+      <c r="F21" t="n">
+        <v>163</v>
+      </c>
+      <c r="G21" t="n">
+        <v>167621</v>
+      </c>
+      <c r="H21" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -10,6 +10,7 @@
     <sheet name="2026-06" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="VWAP_Mensuel" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-05" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-04" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -150,6 +151,23 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_202605" displayName="Table_202605" ref="A1:H21" headerRowCount="1">
+  <autoFilter ref="A1:H21"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_202604" displayName="Table_202604" ref="A1:H21" headerRowCount="1">
   <autoFilter ref="A1:H21"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
@@ -1085,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,20 +1121,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>
@@ -1702,4 +1730,583 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B2" t="n">
+        <v>116.4690246582031</v>
+      </c>
+      <c r="C2" t="n">
+        <v>118.5999984741211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>119.8000030517578</v>
+      </c>
+      <c r="E2" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>142010</v>
+      </c>
+      <c r="H2" t="n">
+        <v>118.5999984741211</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B3" t="n">
+        <v>116.0762100219727</v>
+      </c>
+      <c r="C3" t="n">
+        <v>118.1999969482422</v>
+      </c>
+      <c r="D3" t="n">
+        <v>118.1999969482422</v>
+      </c>
+      <c r="E3" t="n">
+        <v>114.3000030517578</v>
+      </c>
+      <c r="F3" t="n">
+        <v>117.1999969482422</v>
+      </c>
+      <c r="G3" t="n">
+        <v>115896</v>
+      </c>
+      <c r="H3" t="n">
+        <v>118.4202485774794</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B4" t="n">
+        <v>115.4869918823242</v>
+      </c>
+      <c r="C4" t="n">
+        <v>117.5999984741211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>120.9000015258789</v>
+      </c>
+      <c r="E4" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>118</v>
+      </c>
+      <c r="G4" t="n">
+        <v>143015</v>
+      </c>
+      <c r="H4" t="n">
+        <v>118.1276521095174</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B5" t="n">
+        <v>125.1109085083008</v>
+      </c>
+      <c r="C5" t="n">
+        <v>127.4000015258789</v>
+      </c>
+      <c r="D5" t="n">
+        <v>127.4000015258789</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122.8000030517578</v>
+      </c>
+      <c r="F5" t="n">
+        <v>125.3000030517578</v>
+      </c>
+      <c r="G5" t="n">
+        <v>175393</v>
+      </c>
+      <c r="H5" t="n">
+        <v>120.9495602727477</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B6" t="n">
+        <v>126.4857559204102</v>
+      </c>
+      <c r="C6" t="n">
+        <v>128.8000030517578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>129.1000061035156</v>
+      </c>
+      <c r="E6" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>126.6999969482422</v>
+      </c>
+      <c r="G6" t="n">
+        <v>112534</v>
+      </c>
+      <c r="H6" t="n">
+        <v>122.2320518059932</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B7" t="n">
+        <v>128.7444305419922</v>
+      </c>
+      <c r="C7" t="n">
+        <v>131.1000061035156</v>
+      </c>
+      <c r="D7" t="n">
+        <v>131.8999938964844</v>
+      </c>
+      <c r="E7" t="n">
+        <v>128.8999938964844</v>
+      </c>
+      <c r="F7" t="n">
+        <v>129.1000061035156</v>
+      </c>
+      <c r="G7" t="n">
+        <v>169473</v>
+      </c>
+      <c r="H7" t="n">
+        <v>123.9830037443287</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B8" t="n">
+        <v>127.2713851928711</v>
+      </c>
+      <c r="C8" t="n">
+        <v>129.6000061035156</v>
+      </c>
+      <c r="D8" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>127.4000015258789</v>
+      </c>
+      <c r="F8" t="n">
+        <v>128</v>
+      </c>
+      <c r="G8" t="n">
+        <v>194884</v>
+      </c>
+      <c r="H8" t="n">
+        <v>125.0223682438969</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B9" t="n">
+        <v>130.9049072265625</v>
+      </c>
+      <c r="C9" t="n">
+        <v>133.3000030517578</v>
+      </c>
+      <c r="D9" t="n">
+        <v>133.6000061035156</v>
+      </c>
+      <c r="E9" t="n">
+        <v>129.8999938964844</v>
+      </c>
+      <c r="F9" t="n">
+        <v>130</v>
+      </c>
+      <c r="G9" t="n">
+        <v>146328</v>
+      </c>
+      <c r="H9" t="n">
+        <v>126.0321360003194</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B10" t="n">
+        <v>132.0833435058594</v>
+      </c>
+      <c r="C10" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>136.1000061035156</v>
+      </c>
+      <c r="E10" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>132.6999969482422</v>
+      </c>
+      <c r="G10" t="n">
+        <v>167416</v>
+      </c>
+      <c r="H10" t="n">
+        <v>127.069230960973</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B11" t="n">
+        <v>133.9491882324219</v>
+      </c>
+      <c r="C11" t="n">
+        <v>136.3999938964844</v>
+      </c>
+      <c r="D11" t="n">
+        <v>137.6999969482422</v>
+      </c>
+      <c r="E11" t="n">
+        <v>135</v>
+      </c>
+      <c r="F11" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>184198</v>
+      </c>
+      <c r="H11" t="n">
+        <v>128.1772548111918</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B12" t="n">
+        <v>136.5024871826172</v>
+      </c>
+      <c r="C12" t="n">
+        <v>139</v>
+      </c>
+      <c r="D12" t="n">
+        <v>140.1000061035156</v>
+      </c>
+      <c r="E12" t="n">
+        <v>135.8999938964844</v>
+      </c>
+      <c r="F12" t="n">
+        <v>136.3999938964844</v>
+      </c>
+      <c r="G12" t="n">
+        <v>196319</v>
+      </c>
+      <c r="H12" t="n">
+        <v>129.3931356997022</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B13" t="n">
+        <v>134.5384216308594</v>
+      </c>
+      <c r="C13" t="n">
+        <v>137</v>
+      </c>
+      <c r="D13" t="n">
+        <v>138.1999969482422</v>
+      </c>
+      <c r="E13" t="n">
+        <v>136.8999938964844</v>
+      </c>
+      <c r="F13" t="n">
+        <v>137.8000030517578</v>
+      </c>
+      <c r="G13" t="n">
+        <v>90691</v>
+      </c>
+      <c r="H13" t="n">
+        <v>129.7684432116602</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B14" t="n">
+        <v>133.2617645263672</v>
+      </c>
+      <c r="C14" t="n">
+        <v>135.6999969482422</v>
+      </c>
+      <c r="D14" t="n">
+        <v>138.6999969482422</v>
+      </c>
+      <c r="E14" t="n">
+        <v>135.6999969482422</v>
+      </c>
+      <c r="F14" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>138365</v>
+      </c>
+      <c r="H14" t="n">
+        <v>130.183677361729</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B15" t="n">
+        <v>133.0653686523438</v>
+      </c>
+      <c r="C15" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>138.8000030517578</v>
+      </c>
+      <c r="E15" t="n">
+        <v>135.3999938964844</v>
+      </c>
+      <c r="F15" t="n">
+        <v>137</v>
+      </c>
+      <c r="G15" t="n">
+        <v>142311</v>
+      </c>
+      <c r="H15" t="n">
+        <v>130.5407471218162</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B16" t="n">
+        <v>132.4761505126953</v>
+      </c>
+      <c r="C16" t="n">
+        <v>134.8999938964844</v>
+      </c>
+      <c r="D16" t="n">
+        <v>135.8000030517578</v>
+      </c>
+      <c r="E16" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="F16" t="n">
+        <v>134</v>
+      </c>
+      <c r="G16" t="n">
+        <v>167614</v>
+      </c>
+      <c r="H16" t="n">
+        <v>130.86031315107</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B17" t="n">
+        <v>135.0294342041016</v>
+      </c>
+      <c r="C17" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>137.6000061035156</v>
+      </c>
+      <c r="E17" t="n">
+        <v>133.3000030517578</v>
+      </c>
+      <c r="F17" t="n">
+        <v>133.6999969482422</v>
+      </c>
+      <c r="G17" t="n">
+        <v>155302</v>
+      </c>
+      <c r="H17" t="n">
+        <v>131.2826156264729</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B18" t="n">
+        <v>134.3420104980469</v>
+      </c>
+      <c r="C18" t="n">
+        <v>136.8000030517578</v>
+      </c>
+      <c r="D18" t="n">
+        <v>140.1999969482422</v>
+      </c>
+      <c r="E18" t="n">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="F18" t="n">
+        <v>137.6999969482422</v>
+      </c>
+      <c r="G18" t="n">
+        <v>118173</v>
+      </c>
+      <c r="H18" t="n">
+        <v>131.5373133181245</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B19" t="n">
+        <v>145.3407745361328</v>
+      </c>
+      <c r="C19" t="n">
+        <v>148</v>
+      </c>
+      <c r="D19" t="n">
+        <v>149.8999938964844</v>
+      </c>
+      <c r="E19" t="n">
+        <v>139.3999938964844</v>
+      </c>
+      <c r="F19" t="n">
+        <v>140</v>
+      </c>
+      <c r="G19" t="n">
+        <v>379621</v>
+      </c>
+      <c r="H19" t="n">
+        <v>133.6633518148773</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B20" t="n">
+        <v>150.3491363525391</v>
+      </c>
+      <c r="C20" t="n">
+        <v>153.1000061035156</v>
+      </c>
+      <c r="D20" t="n">
+        <v>154.6999969482422</v>
+      </c>
+      <c r="E20" t="n">
+        <v>146.3000030517578</v>
+      </c>
+      <c r="F20" t="n">
+        <v>147.8999938964844</v>
+      </c>
+      <c r="G20" t="n">
+        <v>233532</v>
+      </c>
+      <c r="H20" t="n">
+        <v>135.0938508573942</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B21" t="n">
+        <v>155.2593078613281</v>
+      </c>
+      <c r="C21" t="n">
+        <v>158.1000061035156</v>
+      </c>
+      <c r="D21" t="n">
+        <v>160.6000061035156</v>
+      </c>
+      <c r="E21" t="n">
+        <v>150.1999969482422</v>
+      </c>
+      <c r="F21" t="n">
+        <v>151.8999938964844</v>
+      </c>
+      <c r="G21" t="n">
+        <v>246312</v>
+      </c>
+      <c r="H21" t="n">
+        <v>136.7510754157676</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -11,6 +11,7 @@
     <sheet name="VWAP_Mensuel" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-05" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-04" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-03" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -169,6 +170,23 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_202604" displayName="Table_202604" ref="A1:H21" headerRowCount="1">
   <autoFilter ref="A1:H21"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table_202603" displayName="Table_202603" ref="A1:H23" headerRowCount="1">
+  <autoFilter ref="A1:H23"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -1103,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,30 +1139,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>136.7510754157676</v>
+        <v>118.5205469791241</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>
@@ -2309,4 +2337,635 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B2" t="n">
+        <v>120.3971481323242</v>
+      </c>
+      <c r="C2" t="n">
+        <v>122.5999984741211</v>
+      </c>
+      <c r="D2" t="n">
+        <v>122.6999969482422</v>
+      </c>
+      <c r="E2" t="n">
+        <v>119.0999984741211</v>
+      </c>
+      <c r="F2" t="n">
+        <v>120.5999984741211</v>
+      </c>
+      <c r="G2" t="n">
+        <v>191432</v>
+      </c>
+      <c r="H2" t="n">
+        <v>122.5999984741211</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B3" t="n">
+        <v>114.603157043457</v>
+      </c>
+      <c r="C3" t="n">
+        <v>116.6999969482422</v>
+      </c>
+      <c r="D3" t="n">
+        <v>121</v>
+      </c>
+      <c r="E3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F3" t="n">
+        <v>121</v>
+      </c>
+      <c r="G3" t="n">
+        <v>230731</v>
+      </c>
+      <c r="H3" t="n">
+        <v>119.3753832139785</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B4" t="n">
+        <v>122.361213684082</v>
+      </c>
+      <c r="C4" t="n">
+        <v>124.5999984741211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>124.6999969482422</v>
+      </c>
+      <c r="E4" t="n">
+        <v>119.4000015258789</v>
+      </c>
+      <c r="F4" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>255106</v>
+      </c>
+      <c r="H4" t="n">
+        <v>121.3433319914273</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B5" t="n">
+        <v>121.5755920410156</v>
+      </c>
+      <c r="C5" t="n">
+        <v>123.8000030517578</v>
+      </c>
+      <c r="D5" t="n">
+        <v>126.3000030517578</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122.6999969482422</v>
+      </c>
+      <c r="F5" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>284174</v>
+      </c>
+      <c r="H5" t="n">
+        <v>122.0694510040971</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B6" t="n">
+        <v>118.4330902099609</v>
+      </c>
+      <c r="C6" t="n">
+        <v>120.5999984741211</v>
+      </c>
+      <c r="D6" t="n">
+        <v>124.5999984741211</v>
+      </c>
+      <c r="E6" t="n">
+        <v>118.8000030517578</v>
+      </c>
+      <c r="F6" t="n">
+        <v>124.1999969482422</v>
+      </c>
+      <c r="G6" t="n">
+        <v>186278</v>
+      </c>
+      <c r="H6" t="n">
+        <v>121.8309551689779</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B7" t="n">
+        <v>116.3708190917969</v>
+      </c>
+      <c r="C7" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>119.1999969482422</v>
+      </c>
+      <c r="E7" t="n">
+        <v>116.0999984741211</v>
+      </c>
+      <c r="F7" t="n">
+        <v>116.8000030517578</v>
+      </c>
+      <c r="G7" t="n">
+        <v>169875</v>
+      </c>
+      <c r="H7" t="n">
+        <v>121.4015018241513</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B8" t="n">
+        <v>118.9241027832031</v>
+      </c>
+      <c r="C8" t="n">
+        <v>121.0999984741211</v>
+      </c>
+      <c r="D8" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="E8" t="n">
+        <v>121.0999984741211</v>
+      </c>
+      <c r="F8" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="G8" t="n">
+        <v>155450</v>
+      </c>
+      <c r="H8" t="n">
+        <v>121.3696842870465</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B9" t="n">
+        <v>117.3528518676758</v>
+      </c>
+      <c r="C9" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>120.8000030517578</v>
+      </c>
+      <c r="E9" t="n">
+        <v>117.9000015258789</v>
+      </c>
+      <c r="F9" t="n">
+        <v>120.8000030517578</v>
+      </c>
+      <c r="G9" t="n">
+        <v>109250</v>
+      </c>
+      <c r="H9" t="n">
+        <v>121.2405914950784</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B10" t="n">
+        <v>116.3708190917969</v>
+      </c>
+      <c r="C10" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>116.5999984741211</v>
+      </c>
+      <c r="F10" t="n">
+        <v>119</v>
+      </c>
+      <c r="G10" t="n">
+        <v>126658</v>
+      </c>
+      <c r="H10" t="n">
+        <v>121.0374743616836</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B11" t="n">
+        <v>115.7816009521484</v>
+      </c>
+      <c r="C11" t="n">
+        <v>117.9000015258789</v>
+      </c>
+      <c r="D11" t="n">
+        <v>120</v>
+      </c>
+      <c r="E11" t="n">
+        <v>117.0999984741211</v>
+      </c>
+      <c r="F11" t="n">
+        <v>117.4000015258789</v>
+      </c>
+      <c r="G11" t="n">
+        <v>123183</v>
+      </c>
+      <c r="H11" t="n">
+        <v>120.8265276277151</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B12" t="n">
+        <v>116.9600372314453</v>
+      </c>
+      <c r="C12" t="n">
+        <v>119.0999984741211</v>
+      </c>
+      <c r="D12" t="n">
+        <v>120.0999984741211</v>
+      </c>
+      <c r="E12" t="n">
+        <v>117.3000030517578</v>
+      </c>
+      <c r="F12" t="n">
+        <v>118.0999984741211</v>
+      </c>
+      <c r="G12" t="n">
+        <v>151709</v>
+      </c>
+      <c r="H12" t="n">
+        <v>120.6944962042262</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B13" t="n">
+        <v>115.0941772460938</v>
+      </c>
+      <c r="C13" t="n">
+        <v>117.1999969482422</v>
+      </c>
+      <c r="D13" t="n">
+        <v>119.4000015258789</v>
+      </c>
+      <c r="E13" t="n">
+        <v>117.1999969482422</v>
+      </c>
+      <c r="F13" t="n">
+        <v>118.1999969482422</v>
+      </c>
+      <c r="G13" t="n">
+        <v>124637</v>
+      </c>
+      <c r="H13" t="n">
+        <v>120.4879287793202</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B14" t="n">
+        <v>118.1384811401367</v>
+      </c>
+      <c r="C14" t="n">
+        <v>120.3000030517578</v>
+      </c>
+      <c r="D14" t="n">
+        <v>121.9000015258789</v>
+      </c>
+      <c r="E14" t="n">
+        <v>118.3000030517578</v>
+      </c>
+      <c r="F14" t="n">
+        <v>118.3000030517578</v>
+      </c>
+      <c r="G14" t="n">
+        <v>147074</v>
+      </c>
+      <c r="H14" t="n">
+        <v>120.4756750484433</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>113.3265228271484</v>
+      </c>
+      <c r="C15" t="n">
+        <v>115.4000015258789</v>
+      </c>
+      <c r="D15" t="n">
+        <v>118.8000030517578</v>
+      </c>
+      <c r="E15" t="n">
+        <v>114.6999969482422</v>
+      </c>
+      <c r="F15" t="n">
+        <v>118.8000030517578</v>
+      </c>
+      <c r="G15" t="n">
+        <v>140610</v>
+      </c>
+      <c r="H15" t="n">
+        <v>120.177828339926</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110.5768280029297</v>
+      </c>
+      <c r="C16" t="n">
+        <v>112.5999984741211</v>
+      </c>
+      <c r="D16" t="n">
+        <v>117.5999984741211</v>
+      </c>
+      <c r="E16" t="n">
+        <v>112.0999984741211</v>
+      </c>
+      <c r="F16" t="n">
+        <v>116.4000015258789</v>
+      </c>
+      <c r="G16" t="n">
+        <v>164319</v>
+      </c>
+      <c r="H16" t="n">
+        <v>119.6915216677868</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B17" t="n">
+        <v>113.8175354003906</v>
+      </c>
+      <c r="C17" t="n">
+        <v>115.9000015258789</v>
+      </c>
+      <c r="D17" t="n">
+        <v>118.1999969482422</v>
+      </c>
+      <c r="E17" t="n">
+        <v>109.6999969482422</v>
+      </c>
+      <c r="F17" t="n">
+        <v>110.9000015258789</v>
+      </c>
+      <c r="G17" t="n">
+        <v>161492</v>
+      </c>
+      <c r="H17" t="n">
+        <v>119.4665748935083</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B18" t="n">
+        <v>113.5229263305664</v>
+      </c>
+      <c r="C18" t="n">
+        <v>115.5999984741211</v>
+      </c>
+      <c r="D18" t="n">
+        <v>116.4000015258789</v>
+      </c>
+      <c r="E18" t="n">
+        <v>114.0999984741211</v>
+      </c>
+      <c r="F18" t="n">
+        <v>116</v>
+      </c>
+      <c r="G18" t="n">
+        <v>129180</v>
+      </c>
+      <c r="H18" t="n">
+        <v>119.291388410733</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B19" t="n">
+        <v>117.1564483642578</v>
+      </c>
+      <c r="C19" t="n">
+        <v>119.3000030517578</v>
+      </c>
+      <c r="D19" t="n">
+        <v>119.3000030517578</v>
+      </c>
+      <c r="E19" t="n">
+        <v>117</v>
+      </c>
+      <c r="F19" t="n">
+        <v>117</v>
+      </c>
+      <c r="G19" t="n">
+        <v>93169</v>
+      </c>
+      <c r="H19" t="n">
+        <v>119.2916610086781</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B20" t="n">
+        <v>114.1121444702148</v>
+      </c>
+      <c r="C20" t="n">
+        <v>116.1999969482422</v>
+      </c>
+      <c r="D20" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>116.1999969482422</v>
+      </c>
+      <c r="F20" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>99374</v>
+      </c>
+      <c r="H20" t="n">
+        <v>119.1907210594709</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B21" t="n">
+        <v>111.9516754150391</v>
+      </c>
+      <c r="C21" t="n">
+        <v>114</v>
+      </c>
+      <c r="D21" t="n">
+        <v>116.3000030517578</v>
+      </c>
+      <c r="E21" t="n">
+        <v>113.0999984741211</v>
+      </c>
+      <c r="F21" t="n">
+        <v>116.1999969482422</v>
+      </c>
+      <c r="G21" t="n">
+        <v>130733</v>
+      </c>
+      <c r="H21" t="n">
+        <v>118.9769511287469</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B22" t="n">
+        <v>111.9516754150391</v>
+      </c>
+      <c r="C22" t="n">
+        <v>114</v>
+      </c>
+      <c r="D22" t="n">
+        <v>116.3000030517578</v>
+      </c>
+      <c r="E22" t="n">
+        <v>113</v>
+      </c>
+      <c r="F22" t="n">
+        <v>113.1999969482422</v>
+      </c>
+      <c r="G22" t="n">
+        <v>174114</v>
+      </c>
+      <c r="H22" t="n">
+        <v>118.7181652702702</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B23" t="n">
+        <v>112.8355026245117</v>
+      </c>
+      <c r="C23" t="n">
+        <v>114.9000015258789</v>
+      </c>
+      <c r="D23" t="n">
+        <v>115.1999969482422</v>
+      </c>
+      <c r="E23" t="n">
+        <v>111</v>
+      </c>
+      <c r="F23" t="n">
+        <v>113.5999984741211</v>
+      </c>
+      <c r="G23" t="n">
+        <v>182772</v>
+      </c>
+      <c r="H23" t="n">
+        <v>118.5205469791241</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -12,6 +12,7 @@
     <sheet name="2026-05" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-04" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-02" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -187,6 +188,23 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table_202603" displayName="Table_202603" ref="A1:H23" headerRowCount="1">
   <autoFilter ref="A1:H23"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table_202602" displayName="Table_202602" ref="A1:H21" headerRowCount="1">
+  <autoFilter ref="A1:H21"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -1121,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,40 +1157,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>118.5205469791241</v>
+        <v>130.7767901530345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>136.7510754157676</v>
+        <v>118.5205469791241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>
@@ -2968,4 +2996,583 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B2" t="n">
+        <v>130.4138793945312</v>
+      </c>
+      <c r="C2" t="n">
+        <v>132.8000030517578</v>
+      </c>
+      <c r="D2" t="n">
+        <v>134.3000030517578</v>
+      </c>
+      <c r="E2" t="n">
+        <v>129.1999969482422</v>
+      </c>
+      <c r="F2" t="n">
+        <v>130.8999938964844</v>
+      </c>
+      <c r="G2" t="n">
+        <v>140201</v>
+      </c>
+      <c r="H2" t="n">
+        <v>132.8000030517578</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B3" t="n">
+        <v>133.4581756591797</v>
+      </c>
+      <c r="C3" t="n">
+        <v>135.8999938964844</v>
+      </c>
+      <c r="D3" t="n">
+        <v>136</v>
+      </c>
+      <c r="E3" t="n">
+        <v>132.6999969482422</v>
+      </c>
+      <c r="F3" t="n">
+        <v>134.1999969482422</v>
+      </c>
+      <c r="G3" t="n">
+        <v>124441</v>
+      </c>
+      <c r="H3" t="n">
+        <v>134.2576929146995</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B4" t="n">
+        <v>133.16357421875</v>
+      </c>
+      <c r="C4" t="n">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="D4" t="n">
+        <v>138.6000061035156</v>
+      </c>
+      <c r="E4" t="n">
+        <v>134.8000030517578</v>
+      </c>
+      <c r="F4" t="n">
+        <v>136.1999969482422</v>
+      </c>
+      <c r="G4" t="n">
+        <v>134470</v>
+      </c>
+      <c r="H4" t="n">
+        <v>134.7099490595914</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B5" t="n">
+        <v>133.5563812255859</v>
+      </c>
+      <c r="C5" t="n">
+        <v>136</v>
+      </c>
+      <c r="D5" t="n">
+        <v>138</v>
+      </c>
+      <c r="E5" t="n">
+        <v>134.8000030517578</v>
+      </c>
+      <c r="F5" t="n">
+        <v>135.1999969482422</v>
+      </c>
+      <c r="G5" t="n">
+        <v>114116</v>
+      </c>
+      <c r="H5" t="n">
+        <v>134.9967912683479</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B6" t="n">
+        <v>136.6006927490234</v>
+      </c>
+      <c r="C6" t="n">
+        <v>139.1000061035156</v>
+      </c>
+      <c r="D6" t="n">
+        <v>140.8500061035156</v>
+      </c>
+      <c r="E6" t="n">
+        <v>134.8999938964844</v>
+      </c>
+      <c r="F6" t="n">
+        <v>135.8999938964844</v>
+      </c>
+      <c r="G6" t="n">
+        <v>140172</v>
+      </c>
+      <c r="H6" t="n">
+        <v>135.8770420027757</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B7" t="n">
+        <v>138.9575653076172</v>
+      </c>
+      <c r="C7" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>141.8000030517578</v>
+      </c>
+      <c r="E7" t="n">
+        <v>138.3000030517578</v>
+      </c>
+      <c r="F7" t="n">
+        <v>140.8000030517578</v>
+      </c>
+      <c r="G7" t="n">
+        <v>115317</v>
+      </c>
+      <c r="H7" t="n">
+        <v>136.7205548265664</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B8" t="n">
+        <v>137.3863067626953</v>
+      </c>
+      <c r="C8" t="n">
+        <v>139.8999938964844</v>
+      </c>
+      <c r="D8" t="n">
+        <v>142.1000061035156</v>
+      </c>
+      <c r="E8" t="n">
+        <v>139.3999938964844</v>
+      </c>
+      <c r="F8" t="n">
+        <v>141.6999969482422</v>
+      </c>
+      <c r="G8" t="n">
+        <v>133536</v>
+      </c>
+      <c r="H8" t="n">
+        <v>137.1911208159736</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B9" t="n">
+        <v>139.6449890136719</v>
+      </c>
+      <c r="C9" t="n">
+        <v>142.1999969482422</v>
+      </c>
+      <c r="D9" t="n">
+        <v>144.3000030517578</v>
+      </c>
+      <c r="E9" t="n">
+        <v>139.6000061035156</v>
+      </c>
+      <c r="F9" t="n">
+        <v>139.8999938964844</v>
+      </c>
+      <c r="G9" t="n">
+        <v>96792</v>
+      </c>
+      <c r="H9" t="n">
+        <v>137.6764033994353</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B10" t="n">
+        <v>137.7791290283203</v>
+      </c>
+      <c r="C10" t="n">
+        <v>140.3000030517578</v>
+      </c>
+      <c r="D10" t="n">
+        <v>145.3000030517578</v>
+      </c>
+      <c r="E10" t="n">
+        <v>140</v>
+      </c>
+      <c r="F10" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>135658</v>
+      </c>
+      <c r="H10" t="n">
+        <v>137.9900645791755</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B11" t="n">
+        <v>135.1276397705078</v>
+      </c>
+      <c r="C11" t="n">
+        <v>137.6000061035156</v>
+      </c>
+      <c r="D11" t="n">
+        <v>140</v>
+      </c>
+      <c r="E11" t="n">
+        <v>134.1999969482422</v>
+      </c>
+      <c r="F11" t="n">
+        <v>140</v>
+      </c>
+      <c r="G11" t="n">
+        <v>163746</v>
+      </c>
+      <c r="H11" t="n">
+        <v>137.9408747263932</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B12" t="n">
+        <v>134.9312286376953</v>
+      </c>
+      <c r="C12" t="n">
+        <v>137.3999938964844</v>
+      </c>
+      <c r="D12" t="n">
+        <v>139.3000030517578</v>
+      </c>
+      <c r="E12" t="n">
+        <v>137.1000061035156</v>
+      </c>
+      <c r="F12" t="n">
+        <v>138</v>
+      </c>
+      <c r="G12" t="n">
+        <v>118603</v>
+      </c>
+      <c r="H12" t="n">
+        <v>137.8956046240471</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B13" t="n">
+        <v>135.5204467773438</v>
+      </c>
+      <c r="C13" t="n">
+        <v>138</v>
+      </c>
+      <c r="D13" t="n">
+        <v>138.8999938964844</v>
+      </c>
+      <c r="E13" t="n">
+        <v>135.8999938964844</v>
+      </c>
+      <c r="F13" t="n">
+        <v>137.3000030517578</v>
+      </c>
+      <c r="G13" t="n">
+        <v>230670</v>
+      </c>
+      <c r="H13" t="n">
+        <v>137.9102192746806</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B14" t="n">
+        <v>134.0473937988281</v>
+      </c>
+      <c r="C14" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>139</v>
+      </c>
+      <c r="E14" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>138.3000030517578</v>
+      </c>
+      <c r="G14" t="n">
+        <v>210067</v>
+      </c>
+      <c r="H14" t="n">
+        <v>137.750760621209</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B15" t="n">
+        <v>124.3252792358398</v>
+      </c>
+      <c r="C15" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="D15" t="n">
+        <v>134.6999969482422</v>
+      </c>
+      <c r="E15" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="F15" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="G15" t="n">
+        <v>426298</v>
+      </c>
+      <c r="H15" t="n">
+        <v>135.6696018904867</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B16" t="n">
+        <v>123.8342666625977</v>
+      </c>
+      <c r="C16" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="D16" t="n">
+        <v>129</v>
+      </c>
+      <c r="E16" t="n">
+        <v>125.1999969482422</v>
+      </c>
+      <c r="F16" t="n">
+        <v>126.6999969482422</v>
+      </c>
+      <c r="G16" t="n">
+        <v>192971</v>
+      </c>
+      <c r="H16" t="n">
+        <v>134.9240981756526</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B17" t="n">
+        <v>120.691764831543</v>
+      </c>
+      <c r="C17" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="D17" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="E17" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="F17" t="n">
+        <v>124.5999984741211</v>
+      </c>
+      <c r="G17" t="n">
+        <v>158163</v>
+      </c>
+      <c r="H17" t="n">
+        <v>134.2024254209128</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B18" t="n">
+        <v>118.236686706543</v>
+      </c>
+      <c r="C18" t="n">
+        <v>120.4000015258789</v>
+      </c>
+      <c r="D18" t="n">
+        <v>121.1999969482422</v>
+      </c>
+      <c r="E18" t="n">
+        <v>118.0999984741211</v>
+      </c>
+      <c r="F18" t="n">
+        <v>118.8000030517578</v>
+      </c>
+      <c r="G18" t="n">
+        <v>332314</v>
+      </c>
+      <c r="H18" t="n">
+        <v>132.6567861296309</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B19" t="n">
+        <v>120.2007446289062</v>
+      </c>
+      <c r="C19" t="n">
+        <v>122.4000015258789</v>
+      </c>
+      <c r="D19" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="E19" t="n">
+        <v>120.4000015258789</v>
+      </c>
+      <c r="F19" t="n">
+        <v>121</v>
+      </c>
+      <c r="G19" t="n">
+        <v>191694</v>
+      </c>
+      <c r="H19" t="n">
+        <v>132.0344304637923</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B20" t="n">
+        <v>119.2187118530273</v>
+      </c>
+      <c r="C20" t="n">
+        <v>121.4000015258789</v>
+      </c>
+      <c r="D20" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="E20" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="F20" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="G20" t="n">
+        <v>193103</v>
+      </c>
+      <c r="H20" t="n">
+        <v>131.4218598320059</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B21" t="n">
+        <v>120.1025466918945</v>
+      </c>
+      <c r="C21" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="D21" t="n">
+        <v>123.6999969482422</v>
+      </c>
+      <c r="E21" t="n">
+        <v>121.4000015258789</v>
+      </c>
+      <c r="F21" t="n">
+        <v>121.4000015258789</v>
+      </c>
+      <c r="G21" t="n">
+        <v>255107</v>
+      </c>
+      <c r="H21" t="n">
+        <v>130.7767901530345</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -13,6 +13,7 @@
     <sheet name="2026-04" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-03" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-02" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-01" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -205,6 +206,23 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table_202602" displayName="Table_202602" ref="A1:H21" headerRowCount="1">
   <autoFilter ref="A1:H21"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table_202601" displayName="Table_202601" ref="A1:H22" headerRowCount="1">
+  <autoFilter ref="A1:H22"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -1139,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,50 +1175,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>130.7767901530345</v>
+        <v>127.2027482625323</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>118.5205469791241</v>
+        <v>130.7767901530345</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>136.7510754157676</v>
+        <v>118.5205469791241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>
@@ -3575,4 +3603,609 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B2" t="n">
+        <v>125.9947357177734</v>
+      </c>
+      <c r="C2" t="n">
+        <v>128.3000030517578</v>
+      </c>
+      <c r="D2" t="n">
+        <v>128.6000061035156</v>
+      </c>
+      <c r="E2" t="n">
+        <v>125.8000030517578</v>
+      </c>
+      <c r="F2" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="G2" t="n">
+        <v>82171</v>
+      </c>
+      <c r="H2" t="n">
+        <v>128.3000030517578</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B3" t="n">
+        <v>130.315673828125</v>
+      </c>
+      <c r="C3" t="n">
+        <v>132.6999969482422</v>
+      </c>
+      <c r="D3" t="n">
+        <v>133</v>
+      </c>
+      <c r="E3" t="n">
+        <v>128.6000061035156</v>
+      </c>
+      <c r="F3" t="n">
+        <v>129.3999938964844</v>
+      </c>
+      <c r="G3" t="n">
+        <v>127449</v>
+      </c>
+      <c r="H3" t="n">
+        <v>130.9752001804337</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B4" t="n">
+        <v>124.5216903686523</v>
+      </c>
+      <c r="C4" t="n">
+        <v>126.8000030517578</v>
+      </c>
+      <c r="D4" t="n">
+        <v>131.1999969482422</v>
+      </c>
+      <c r="E4" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="F4" t="n">
+        <v>129</v>
+      </c>
+      <c r="G4" t="n">
+        <v>156011</v>
+      </c>
+      <c r="H4" t="n">
+        <v>129.1936863611956</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B5" t="n">
+        <v>127.2713851928711</v>
+      </c>
+      <c r="C5" t="n">
+        <v>129.6000061035156</v>
+      </c>
+      <c r="D5" t="n">
+        <v>131.8000030517578</v>
+      </c>
+      <c r="E5" t="n">
+        <v>126.9000015258789</v>
+      </c>
+      <c r="F5" t="n">
+        <v>127.4000015258789</v>
+      </c>
+      <c r="G5" t="n">
+        <v>91195</v>
+      </c>
+      <c r="H5" t="n">
+        <v>129.2747989268133</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B6" t="n">
+        <v>123.5396575927734</v>
+      </c>
+      <c r="C6" t="n">
+        <v>125.8000030517578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>129.1999969482422</v>
+      </c>
+      <c r="E6" t="n">
+        <v>125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>129.1999969482422</v>
+      </c>
+      <c r="G6" t="n">
+        <v>106026</v>
+      </c>
+      <c r="H6" t="n">
+        <v>128.6202419430082</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B7" t="n">
+        <v>123.3432464599609</v>
+      </c>
+      <c r="C7" t="n">
+        <v>125.5999984741211</v>
+      </c>
+      <c r="D7" t="n">
+        <v>126.4000015258789</v>
+      </c>
+      <c r="E7" t="n">
+        <v>123.5999984741211</v>
+      </c>
+      <c r="F7" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="G7" t="n">
+        <v>102666</v>
+      </c>
+      <c r="H7" t="n">
+        <v>128.1543246936224</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B8" t="n">
+        <v>120.7899627685547</v>
+      </c>
+      <c r="C8" t="n">
+        <v>123</v>
+      </c>
+      <c r="D8" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="F8" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>150072</v>
+      </c>
+      <c r="H8" t="n">
+        <v>127.2059072100568</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B9" t="n">
+        <v>121.6737976074219</v>
+      </c>
+      <c r="C9" t="n">
+        <v>123.9000015258789</v>
+      </c>
+      <c r="D9" t="n">
+        <v>124.6999969482422</v>
+      </c>
+      <c r="E9" t="n">
+        <v>121.9000015258789</v>
+      </c>
+      <c r="F9" t="n">
+        <v>123.1999969482422</v>
+      </c>
+      <c r="G9" t="n">
+        <v>110839</v>
+      </c>
+      <c r="H9" t="n">
+        <v>126.8103849626653</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B10" t="n">
+        <v>121.6737976074219</v>
+      </c>
+      <c r="C10" t="n">
+        <v>123.9000015258789</v>
+      </c>
+      <c r="D10" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="E10" t="n">
+        <v>122.4000015258789</v>
+      </c>
+      <c r="F10" t="n">
+        <v>123.8000030517578</v>
+      </c>
+      <c r="G10" t="n">
+        <v>113249</v>
+      </c>
+      <c r="H10" t="n">
+        <v>126.4933656414595</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B11" t="n">
+        <v>123.9324645996094</v>
+      </c>
+      <c r="C11" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="D11" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="E11" t="n">
+        <v>123.6999969482422</v>
+      </c>
+      <c r="F11" t="n">
+        <v>124.3000030517578</v>
+      </c>
+      <c r="G11" t="n">
+        <v>133534</v>
+      </c>
+      <c r="H11" t="n">
+        <v>126.459974664313</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B12" t="n">
+        <v>122.0666122436523</v>
+      </c>
+      <c r="C12" t="n">
+        <v>124.3000030517578</v>
+      </c>
+      <c r="D12" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="E12" t="n">
+        <v>124.0999984741211</v>
+      </c>
+      <c r="F12" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="G12" t="n">
+        <v>94424</v>
+      </c>
+      <c r="H12" t="n">
+        <v>126.2990821371648</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B13" t="n">
+        <v>122.9504318237305</v>
+      </c>
+      <c r="C13" t="n">
+        <v>125.1999969482422</v>
+      </c>
+      <c r="D13" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>121.4000015258789</v>
+      </c>
+      <c r="F13" t="n">
+        <v>123.0999984741211</v>
+      </c>
+      <c r="G13" t="n">
+        <v>134351</v>
+      </c>
+      <c r="H13" t="n">
+        <v>126.1937579121778</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B14" t="n">
+        <v>121.6737976074219</v>
+      </c>
+      <c r="C14" t="n">
+        <v>123.9000015258789</v>
+      </c>
+      <c r="D14" t="n">
+        <v>124.5999984741211</v>
+      </c>
+      <c r="E14" t="n">
+        <v>120.9000015258789</v>
+      </c>
+      <c r="F14" t="n">
+        <v>124.5999984741211</v>
+      </c>
+      <c r="G14" t="n">
+        <v>80555</v>
+      </c>
+      <c r="H14" t="n">
+        <v>126.0691249873107</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B15" t="n">
+        <v>121.7719955444336</v>
+      </c>
+      <c r="C15" t="n">
+        <v>124</v>
+      </c>
+      <c r="D15" t="n">
+        <v>125.8000030517578</v>
+      </c>
+      <c r="E15" t="n">
+        <v>122.6999969482422</v>
+      </c>
+      <c r="F15" t="n">
+        <v>124</v>
+      </c>
+      <c r="G15" t="n">
+        <v>126658</v>
+      </c>
+      <c r="H15" t="n">
+        <v>125.9062669009058</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B16" t="n">
+        <v>124.3252792358398</v>
+      </c>
+      <c r="C16" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="D16" t="n">
+        <v>128.6999969482422</v>
+      </c>
+      <c r="E16" t="n">
+        <v>122.1999969482422</v>
+      </c>
+      <c r="F16" t="n">
+        <v>124.6999969482422</v>
+      </c>
+      <c r="G16" t="n">
+        <v>177451</v>
+      </c>
+      <c r="H16" t="n">
+        <v>125.9751686401926</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B17" t="n">
+        <v>125.405517578125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>127.6999969482422</v>
+      </c>
+      <c r="D17" t="n">
+        <v>127.6999969482422</v>
+      </c>
+      <c r="E17" t="n">
+        <v>125.3000030517578</v>
+      </c>
+      <c r="F17" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="G17" t="n">
+        <v>133439</v>
+      </c>
+      <c r="H17" t="n">
+        <v>126.0950376903923</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B18" t="n">
+        <v>125.7001266479492</v>
+      </c>
+      <c r="C18" t="n">
+        <v>128</v>
+      </c>
+      <c r="D18" t="n">
+        <v>128.8000030517578</v>
+      </c>
+      <c r="E18" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="F18" t="n">
+        <v>127.3000030517578</v>
+      </c>
+      <c r="G18" t="n">
+        <v>87006</v>
+      </c>
+      <c r="H18" t="n">
+        <v>126.1776162769221</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B19" t="n">
+        <v>127.3695755004883</v>
+      </c>
+      <c r="C19" t="n">
+        <v>129.6999969482422</v>
+      </c>
+      <c r="D19" t="n">
+        <v>130.8000030517578</v>
+      </c>
+      <c r="E19" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>128.6999969482422</v>
+      </c>
+      <c r="G19" t="n">
+        <v>148370</v>
+      </c>
+      <c r="H19" t="n">
+        <v>126.4200768957413</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B20" t="n">
+        <v>128.4498138427734</v>
+      </c>
+      <c r="C20" t="n">
+        <v>130.8000030517578</v>
+      </c>
+      <c r="D20" t="n">
+        <v>130.8999938964844</v>
+      </c>
+      <c r="E20" t="n">
+        <v>128.8999938964844</v>
+      </c>
+      <c r="F20" t="n">
+        <v>130.6000061035156</v>
+      </c>
+      <c r="G20" t="n">
+        <v>120502</v>
+      </c>
+      <c r="H20" t="n">
+        <v>126.6519737684796</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B21" t="n">
+        <v>128.9408416748047</v>
+      </c>
+      <c r="C21" t="n">
+        <v>131.3000030517578</v>
+      </c>
+      <c r="D21" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>130.3999938964844</v>
+      </c>
+      <c r="F21" t="n">
+        <v>132</v>
+      </c>
+      <c r="G21" t="n">
+        <v>128397</v>
+      </c>
+      <c r="H21" t="n">
+        <v>126.9001860889405</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B22" t="n">
+        <v>130.5120849609375</v>
+      </c>
+      <c r="C22" t="n">
+        <v>132.8999938964844</v>
+      </c>
+      <c r="D22" t="n">
+        <v>133.6000061035156</v>
+      </c>
+      <c r="E22" t="n">
+        <v>130.8000030517578</v>
+      </c>
+      <c r="F22" t="n">
+        <v>131</v>
+      </c>
+      <c r="G22" t="n">
+        <v>127688</v>
+      </c>
+      <c r="H22" t="n">
+        <v>127.2027482625323</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -14,6 +14,7 @@
     <sheet name="2026-03" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-02" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-01" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2025-12" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -222,6 +223,23 @@
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table_202601" displayName="Table_202601" ref="A1:H22" headerRowCount="1">
+  <autoFilter ref="A1:H22"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table_202512" displayName="Table_202512" ref="A1:H22" headerRowCount="1">
   <autoFilter ref="A1:H22"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
@@ -1157,7 +1175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,60 +1193,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>127.2027482625323</v>
+        <v>125.3875453652953</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>130.7767901530345</v>
+        <v>127.2027482625323</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>118.5205469791241</v>
+        <v>130.7767901530345</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>136.7510754157676</v>
+        <v>118.5205469791241</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>
@@ -4208,4 +4236,609 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B2" t="n">
+        <v>124.1288757324219</v>
+      </c>
+      <c r="C2" t="n">
+        <v>126.4000015258789</v>
+      </c>
+      <c r="D2" t="n">
+        <v>127.1999969482422</v>
+      </c>
+      <c r="E2" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="F2" t="n">
+        <v>124.5999984741211</v>
+      </c>
+      <c r="G2" t="n">
+        <v>145425</v>
+      </c>
+      <c r="H2" t="n">
+        <v>126.4000015258789</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B3" t="n">
+        <v>125.3073120117188</v>
+      </c>
+      <c r="C3" t="n">
+        <v>127.5999984741211</v>
+      </c>
+      <c r="D3" t="n">
+        <v>127.8000030517578</v>
+      </c>
+      <c r="E3" t="n">
+        <v>125.6999969482422</v>
+      </c>
+      <c r="F3" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="G3" t="n">
+        <v>85562</v>
+      </c>
+      <c r="H3" t="n">
+        <v>126.8445033328442</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B4" t="n">
+        <v>125.8965301513672</v>
+      </c>
+      <c r="C4" t="n">
+        <v>128.1999969482422</v>
+      </c>
+      <c r="D4" t="n">
+        <v>128.6999969482422</v>
+      </c>
+      <c r="E4" t="n">
+        <v>125.1999969482422</v>
+      </c>
+      <c r="F4" t="n">
+        <v>127.9000015258789</v>
+      </c>
+      <c r="G4" t="n">
+        <v>118533</v>
+      </c>
+      <c r="H4" t="n">
+        <v>127.3041929778258</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B5" t="n">
+        <v>127.5659790039062</v>
+      </c>
+      <c r="C5" t="n">
+        <v>129.8999938964844</v>
+      </c>
+      <c r="D5" t="n">
+        <v>130.6999969482422</v>
+      </c>
+      <c r="E5" t="n">
+        <v>128.3999938964844</v>
+      </c>
+      <c r="F5" t="n">
+        <v>129.3999938964844</v>
+      </c>
+      <c r="G5" t="n">
+        <v>129705</v>
+      </c>
+      <c r="H5" t="n">
+        <v>128.0067614125999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B6" t="n">
+        <v>127.2713851928711</v>
+      </c>
+      <c r="C6" t="n">
+        <v>129.6000061035156</v>
+      </c>
+      <c r="D6" t="n">
+        <v>131.6999969482422</v>
+      </c>
+      <c r="E6" t="n">
+        <v>129.6000061035156</v>
+      </c>
+      <c r="F6" t="n">
+        <v>130.1999969482422</v>
+      </c>
+      <c r="G6" t="n">
+        <v>118357</v>
+      </c>
+      <c r="H6" t="n">
+        <v>128.3223192136761</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B7" t="n">
+        <v>129.3336486816406</v>
+      </c>
+      <c r="C7" t="n">
+        <v>131.6999969482422</v>
+      </c>
+      <c r="D7" t="n">
+        <v>132.1000061035156</v>
+      </c>
+      <c r="E7" t="n">
+        <v>129.6000061035156</v>
+      </c>
+      <c r="F7" t="n">
+        <v>129.8000030517578</v>
+      </c>
+      <c r="G7" t="n">
+        <v>72543</v>
+      </c>
+      <c r="H7" t="n">
+        <v>128.6879627516707</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B8" t="n">
+        <v>121.0845794677734</v>
+      </c>
+      <c r="C8" t="n">
+        <v>123.3000030517578</v>
+      </c>
+      <c r="D8" t="n">
+        <v>132</v>
+      </c>
+      <c r="E8" t="n">
+        <v>115.1999969482422</v>
+      </c>
+      <c r="F8" t="n">
+        <v>131.8000030517578</v>
+      </c>
+      <c r="G8" t="n">
+        <v>339747</v>
+      </c>
+      <c r="H8" t="n">
+        <v>126.8753140752381</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B9" t="n">
+        <v>125.405517578125</v>
+      </c>
+      <c r="C9" t="n">
+        <v>127.6999969482422</v>
+      </c>
+      <c r="D9" t="n">
+        <v>128.3000030517578</v>
+      </c>
+      <c r="E9" t="n">
+        <v>123.8000030517578</v>
+      </c>
+      <c r="F9" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>197050</v>
+      </c>
+      <c r="H9" t="n">
+        <v>127.0099572088669</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B10" t="n">
+        <v>123.7360610961914</v>
+      </c>
+      <c r="C10" t="n">
+        <v>126</v>
+      </c>
+      <c r="D10" t="n">
+        <v>128.1999969482422</v>
+      </c>
+      <c r="E10" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="F10" t="n">
+        <v>128</v>
+      </c>
+      <c r="G10" t="n">
+        <v>163523</v>
+      </c>
+      <c r="H10" t="n">
+        <v>126.8894480073553</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B11" t="n">
+        <v>121.2809829711914</v>
+      </c>
+      <c r="C11" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>127</v>
+      </c>
+      <c r="G11" t="n">
+        <v>170496</v>
+      </c>
+      <c r="H11" t="n">
+        <v>126.5144256492883</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B12" t="n">
+        <v>123.4414520263672</v>
+      </c>
+      <c r="C12" t="n">
+        <v>125.6999969482422</v>
+      </c>
+      <c r="D12" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="E12" t="n">
+        <v>123.5999984741211</v>
+      </c>
+      <c r="F12" t="n">
+        <v>124</v>
+      </c>
+      <c r="G12" t="n">
+        <v>120738</v>
+      </c>
+      <c r="H12" t="n">
+        <v>126.4552490619289</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>121.5755920410156</v>
+      </c>
+      <c r="C13" t="n">
+        <v>123.8000030517578</v>
+      </c>
+      <c r="D13" t="n">
+        <v>125.5999984741211</v>
+      </c>
+      <c r="E13" t="n">
+        <v>123.8000030517578</v>
+      </c>
+      <c r="F13" t="n">
+        <v>124.8000030517578</v>
+      </c>
+      <c r="G13" t="n">
+        <v>93442</v>
+      </c>
+      <c r="H13" t="n">
+        <v>126.3138847356617</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B14" t="n">
+        <v>118.236686706543</v>
+      </c>
+      <c r="C14" t="n">
+        <v>120.4000015258789</v>
+      </c>
+      <c r="D14" t="n">
+        <v>123.9000015258789</v>
+      </c>
+      <c r="E14" t="n">
+        <v>120.4000015258789</v>
+      </c>
+      <c r="F14" t="n">
+        <v>123.8000030517578</v>
+      </c>
+      <c r="G14" t="n">
+        <v>118460</v>
+      </c>
+      <c r="H14" t="n">
+        <v>125.9399705013527</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B15" t="n">
+        <v>120.1025466918945</v>
+      </c>
+      <c r="C15" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="D15" t="n">
+        <v>122.8000030517578</v>
+      </c>
+      <c r="E15" t="n">
+        <v>120</v>
+      </c>
+      <c r="F15" t="n">
+        <v>120</v>
+      </c>
+      <c r="G15" t="n">
+        <v>125857</v>
+      </c>
+      <c r="H15" t="n">
+        <v>125.7108484263978</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B16" t="n">
+        <v>120.2989501953125</v>
+      </c>
+      <c r="C16" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>121.8000030517578</v>
+      </c>
+      <c r="F16" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>178704</v>
+      </c>
+      <c r="H16" t="n">
+        <v>125.4474168148725</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B17" t="n">
+        <v>122.1648101806641</v>
+      </c>
+      <c r="C17" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="D17" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="E17" t="n">
+        <v>122.0999984741211</v>
+      </c>
+      <c r="F17" t="n">
+        <v>122.6999969482422</v>
+      </c>
+      <c r="G17" t="n">
+        <v>112307</v>
+      </c>
+      <c r="H17" t="n">
+        <v>125.3960591688996</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B18" t="n">
+        <v>121.9683990478516</v>
+      </c>
+      <c r="C18" t="n">
+        <v>124.1999969482422</v>
+      </c>
+      <c r="D18" t="n">
+        <v>125.9000015258789</v>
+      </c>
+      <c r="E18" t="n">
+        <v>122.6999969482422</v>
+      </c>
+      <c r="F18" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="G18" t="n">
+        <v>69278</v>
+      </c>
+      <c r="H18" t="n">
+        <v>125.3609445990689</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B19" t="n">
+        <v>122.5576248168945</v>
+      </c>
+      <c r="C19" t="n">
+        <v>124.8000030517578</v>
+      </c>
+      <c r="D19" t="n">
+        <v>125.3000030517578</v>
+      </c>
+      <c r="E19" t="n">
+        <v>123.9000015258789</v>
+      </c>
+      <c r="F19" t="n">
+        <v>124.1999969482422</v>
+      </c>
+      <c r="G19" t="n">
+        <v>28633</v>
+      </c>
+      <c r="H19" t="n">
+        <v>125.3542197170059</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B20" t="n">
+        <v>123.2450485229492</v>
+      </c>
+      <c r="C20" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="E20" t="n">
+        <v>123.8000030517578</v>
+      </c>
+      <c r="F20" t="n">
+        <v>125.3000030517578</v>
+      </c>
+      <c r="G20" t="n">
+        <v>68673</v>
+      </c>
+      <c r="H20" t="n">
+        <v>125.358294212291</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B21" t="n">
+        <v>124.3252792358398</v>
+      </c>
+      <c r="C21" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="D21" t="n">
+        <v>127</v>
+      </c>
+      <c r="E21" t="n">
+        <v>125.1999969482422</v>
+      </c>
+      <c r="F21" t="n">
+        <v>125.5999984741211</v>
+      </c>
+      <c r="G21" t="n">
+        <v>43667</v>
+      </c>
+      <c r="H21" t="n">
+        <v>125.3799767411835</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B22" t="n">
+        <v>123.5396575927734</v>
+      </c>
+      <c r="C22" t="n">
+        <v>125.8000030517578</v>
+      </c>
+      <c r="D22" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="E22" t="n">
+        <v>125.3000030517578</v>
+      </c>
+      <c r="F22" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="G22" t="n">
+        <v>45888</v>
+      </c>
+      <c r="H22" t="n">
+        <v>125.3875453652953</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -15,6 +15,7 @@
     <sheet name="2026-02" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-01" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2025-12" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2025-11" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -241,6 +242,23 @@
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table_202512" displayName="Table_202512" ref="A1:H22" headerRowCount="1">
   <autoFilter ref="A1:H22"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table_202511" displayName="Table_202511" ref="A1:H21" headerRowCount="1">
+  <autoFilter ref="A1:H21"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -1175,7 +1193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,70 +1211,80 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>125.3875453652953</v>
+        <v>122.0752800594647</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>127.2027482625323</v>
+        <v>125.3875453652953</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>130.7767901530345</v>
+        <v>127.2027482625323</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>118.5205469791241</v>
+        <v>130.7767901530345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>136.7510754157676</v>
+        <v>118.5205469791241</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>
@@ -4841,4 +4869,583 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B2" t="n">
+        <v>119.6115264892578</v>
+      </c>
+      <c r="C2" t="n">
+        <v>121.8000030517578</v>
+      </c>
+      <c r="D2" t="n">
+        <v>123</v>
+      </c>
+      <c r="E2" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="F2" t="n">
+        <v>122</v>
+      </c>
+      <c r="G2" t="n">
+        <v>137323</v>
+      </c>
+      <c r="H2" t="n">
+        <v>121.8000030517578</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B3" t="n">
+        <v>118.236686706543</v>
+      </c>
+      <c r="C3" t="n">
+        <v>120.4000015258789</v>
+      </c>
+      <c r="D3" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>118.4000015258789</v>
+      </c>
+      <c r="F3" t="n">
+        <v>120.1999969482422</v>
+      </c>
+      <c r="G3" t="n">
+        <v>144468</v>
+      </c>
+      <c r="H3" t="n">
+        <v>121.0822532994922</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B4" t="n">
+        <v>123.3432464599609</v>
+      </c>
+      <c r="C4" t="n">
+        <v>125.5999984741211</v>
+      </c>
+      <c r="D4" t="n">
+        <v>126.4000015258789</v>
+      </c>
+      <c r="E4" t="n">
+        <v>119.3000030517578</v>
+      </c>
+      <c r="F4" t="n">
+        <v>119.8000030517578</v>
+      </c>
+      <c r="G4" t="n">
+        <v>151741</v>
+      </c>
+      <c r="H4" t="n">
+        <v>122.663514130396</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B5" t="n">
+        <v>118.8258972167969</v>
+      </c>
+      <c r="C5" t="n">
+        <v>121</v>
+      </c>
+      <c r="D5" t="n">
+        <v>124.5999984741211</v>
+      </c>
+      <c r="E5" t="n">
+        <v>120.5999984741211</v>
+      </c>
+      <c r="F5" t="n">
+        <v>124.1999969482422</v>
+      </c>
+      <c r="G5" t="n">
+        <v>151199</v>
+      </c>
+      <c r="H5" t="n">
+        <v>122.2333647574334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B6" t="n">
+        <v>117.2546539306641</v>
+      </c>
+      <c r="C6" t="n">
+        <v>119.4000015258789</v>
+      </c>
+      <c r="D6" t="n">
+        <v>122</v>
+      </c>
+      <c r="E6" t="n">
+        <v>118.4000015258789</v>
+      </c>
+      <c r="F6" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="G6" t="n">
+        <v>106124</v>
+      </c>
+      <c r="H6" t="n">
+        <v>121.7981245990999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B7" t="n">
+        <v>118.1384811401367</v>
+      </c>
+      <c r="C7" t="n">
+        <v>120.3000030517578</v>
+      </c>
+      <c r="D7" t="n">
+        <v>122.1999969482422</v>
+      </c>
+      <c r="E7" t="n">
+        <v>120.3000030517578</v>
+      </c>
+      <c r="F7" t="n">
+        <v>121.8000030517578</v>
+      </c>
+      <c r="G7" t="n">
+        <v>78724</v>
+      </c>
+      <c r="H7" t="n">
+        <v>121.6448744185558</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B8" t="n">
+        <v>119.1205139160156</v>
+      </c>
+      <c r="C8" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="D8" t="n">
+        <v>121.8000030517578</v>
+      </c>
+      <c r="E8" t="n">
+        <v>119.5999984741211</v>
+      </c>
+      <c r="F8" t="n">
+        <v>120</v>
+      </c>
+      <c r="G8" t="n">
+        <v>124901</v>
+      </c>
+      <c r="H8" t="n">
+        <v>121.5967181952927</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B9" t="n">
+        <v>120.3971481323242</v>
+      </c>
+      <c r="C9" t="n">
+        <v>122.5999984741211</v>
+      </c>
+      <c r="D9" t="n">
+        <v>123.6999969482422</v>
+      </c>
+      <c r="E9" t="n">
+        <v>121.5999984741211</v>
+      </c>
+      <c r="F9" t="n">
+        <v>121.6999969482422</v>
+      </c>
+      <c r="G9" t="n">
+        <v>101868</v>
+      </c>
+      <c r="H9" t="n">
+        <v>121.699294961085</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B10" t="n">
+        <v>120.5935592651367</v>
+      </c>
+      <c r="C10" t="n">
+        <v>122.8000030517578</v>
+      </c>
+      <c r="D10" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="E10" t="n">
+        <v>122</v>
+      </c>
+      <c r="F10" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="G10" t="n">
+        <v>152224</v>
+      </c>
+      <c r="H10" t="n">
+        <v>121.8451754007915</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B11" t="n">
+        <v>119.906135559082</v>
+      </c>
+      <c r="C11" t="n">
+        <v>122.0999984741211</v>
+      </c>
+      <c r="D11" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="E11" t="n">
+        <v>120.0999984741211</v>
+      </c>
+      <c r="F11" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="G11" t="n">
+        <v>102775</v>
+      </c>
+      <c r="H11" t="n">
+        <v>121.8661044007903</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B12" t="n">
+        <v>119.5133209228516</v>
+      </c>
+      <c r="C12" t="n">
+        <v>121.6999969482422</v>
+      </c>
+      <c r="D12" t="n">
+        <v>123.1999969482422</v>
+      </c>
+      <c r="E12" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="F12" t="n">
+        <v>121.4000015258789</v>
+      </c>
+      <c r="G12" t="n">
+        <v>102834</v>
+      </c>
+      <c r="H12" t="n">
+        <v>121.8534905081309</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B13" t="n">
+        <v>116.7636337280273</v>
+      </c>
+      <c r="C13" t="n">
+        <v>118.9000015258789</v>
+      </c>
+      <c r="D13" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="E13" t="n">
+        <v>117.0999984741211</v>
+      </c>
+      <c r="F13" t="n">
+        <v>120.3000030517578</v>
+      </c>
+      <c r="G13" t="n">
+        <v>147129</v>
+      </c>
+      <c r="H13" t="n">
+        <v>121.56404736816</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B14" t="n">
+        <v>123.8342666625977</v>
+      </c>
+      <c r="C14" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="D14" t="n">
+        <v>127.9000015258789</v>
+      </c>
+      <c r="E14" t="n">
+        <v>118.6999969482422</v>
+      </c>
+      <c r="F14" t="n">
+        <v>118.6999969482422</v>
+      </c>
+      <c r="G14" t="n">
+        <v>165813</v>
+      </c>
+      <c r="H14" t="n">
+        <v>122.0151956402028</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B15" t="n">
+        <v>121.1827774047852</v>
+      </c>
+      <c r="C15" t="n">
+        <v>123.4000015258789</v>
+      </c>
+      <c r="D15" t="n">
+        <v>128</v>
+      </c>
+      <c r="E15" t="n">
+        <v>123.4000015258789</v>
+      </c>
+      <c r="F15" t="n">
+        <v>127.9000015258789</v>
+      </c>
+      <c r="G15" t="n">
+        <v>113650</v>
+      </c>
+      <c r="H15" t="n">
+        <v>122.1035747816807</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B16" t="n">
+        <v>117.451057434082</v>
+      </c>
+      <c r="C16" t="n">
+        <v>119.5999984741211</v>
+      </c>
+      <c r="D16" t="n">
+        <v>121.0999984741211</v>
+      </c>
+      <c r="E16" t="n">
+        <v>116.0999984741211</v>
+      </c>
+      <c r="F16" t="n">
+        <v>120.8000030517578</v>
+      </c>
+      <c r="G16" t="n">
+        <v>115469</v>
+      </c>
+      <c r="H16" t="n">
+        <v>121.9511230098828</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B17" t="n">
+        <v>118.3348846435547</v>
+      </c>
+      <c r="C17" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="E17" t="n">
+        <v>120</v>
+      </c>
+      <c r="F17" t="n">
+        <v>120.0999984741211</v>
+      </c>
+      <c r="G17" t="n">
+        <v>183155</v>
+      </c>
+      <c r="H17" t="n">
+        <v>121.8233069002726</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B18" t="n">
+        <v>119.6115264892578</v>
+      </c>
+      <c r="C18" t="n">
+        <v>121.8000030517578</v>
+      </c>
+      <c r="D18" t="n">
+        <v>122.1999969482422</v>
+      </c>
+      <c r="E18" t="n">
+        <v>119.3000030517578</v>
+      </c>
+      <c r="F18" t="n">
+        <v>120.3000030517578</v>
+      </c>
+      <c r="G18" t="n">
+        <v>105858</v>
+      </c>
+      <c r="H18" t="n">
+        <v>121.8221780165514</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B19" t="n">
+        <v>121.0845794677734</v>
+      </c>
+      <c r="C19" t="n">
+        <v>123.3000030517578</v>
+      </c>
+      <c r="D19" t="n">
+        <v>123.4000015258789</v>
+      </c>
+      <c r="E19" t="n">
+        <v>121.8000030517578</v>
+      </c>
+      <c r="F19" t="n">
+        <v>123</v>
+      </c>
+      <c r="G19" t="n">
+        <v>94381</v>
+      </c>
+      <c r="H19" t="n">
+        <v>121.8833626112182</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="B20" t="n">
+        <v>122.6558303833008</v>
+      </c>
+      <c r="C20" t="n">
+        <v>124.9000015258789</v>
+      </c>
+      <c r="D20" t="n">
+        <v>125.0999984741211</v>
+      </c>
+      <c r="E20" t="n">
+        <v>123</v>
+      </c>
+      <c r="F20" t="n">
+        <v>123.4000015258789</v>
+      </c>
+      <c r="G20" t="n">
+        <v>56960</v>
+      </c>
+      <c r="H20" t="n">
+        <v>121.9569002499795</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B21" t="n">
+        <v>122.4594192504883</v>
+      </c>
+      <c r="C21" t="n">
+        <v>124.6999969482422</v>
+      </c>
+      <c r="D21" t="n">
+        <v>125.9000015258789</v>
+      </c>
+      <c r="E21" t="n">
+        <v>124.1999969482422</v>
+      </c>
+      <c r="F21" t="n">
+        <v>125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>105385</v>
+      </c>
+      <c r="H21" t="n">
+        <v>122.0752800594647</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -16,6 +16,7 @@
     <sheet name="2026-01" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2025-12" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2025-11" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2025-10" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -259,6 +260,23 @@
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table_202511" displayName="Table_202511" ref="A1:H21" headerRowCount="1">
   <autoFilter ref="A1:H21"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Table_202510" displayName="Table_202510" ref="A1:H24" headerRowCount="1">
+  <autoFilter ref="A1:H24"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -1187,13 +1205,670 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B2" t="n">
+        <v>126.7803649902344</v>
+      </c>
+      <c r="C2" t="n">
+        <v>129.1000061035156</v>
+      </c>
+      <c r="D2" t="n">
+        <v>129.1999969482422</v>
+      </c>
+      <c r="E2" t="n">
+        <v>126.3000030517578</v>
+      </c>
+      <c r="F2" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="G2" t="n">
+        <v>110982</v>
+      </c>
+      <c r="H2" t="n">
+        <v>129.1000061035156</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B3" t="n">
+        <v>129.0390319824219</v>
+      </c>
+      <c r="C3" t="n">
+        <v>131.3999938964844</v>
+      </c>
+      <c r="D3" t="n">
+        <v>131.6000061035156</v>
+      </c>
+      <c r="E3" t="n">
+        <v>128.8999938964844</v>
+      </c>
+      <c r="F3" t="n">
+        <v>130.3000030517578</v>
+      </c>
+      <c r="G3" t="n">
+        <v>112520</v>
+      </c>
+      <c r="H3" t="n">
+        <v>130.2579135337169</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B4" t="n">
+        <v>128.5480194091797</v>
+      </c>
+      <c r="C4" t="n">
+        <v>130.8999938964844</v>
+      </c>
+      <c r="D4" t="n">
+        <v>132.8999938964844</v>
+      </c>
+      <c r="E4" t="n">
+        <v>128.8000030517578</v>
+      </c>
+      <c r="F4" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>121235</v>
+      </c>
+      <c r="H4" t="n">
+        <v>130.4837164291999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B5" t="n">
+        <v>130.4138793945312</v>
+      </c>
+      <c r="C5" t="n">
+        <v>132.8000030517578</v>
+      </c>
+      <c r="D5" t="n">
+        <v>134.3000030517578</v>
+      </c>
+      <c r="E5" t="n">
+        <v>128.8999938964844</v>
+      </c>
+      <c r="F5" t="n">
+        <v>130.8999938964844</v>
+      </c>
+      <c r="G5" t="n">
+        <v>117150</v>
+      </c>
+      <c r="H5" t="n">
+        <v>131.0712042299664</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B6" t="n">
+        <v>124.0306777954102</v>
+      </c>
+      <c r="C6" t="n">
+        <v>126.3000030517578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>130</v>
+      </c>
+      <c r="E6" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="F6" t="n">
+        <v>130</v>
+      </c>
+      <c r="G6" t="n">
+        <v>157176</v>
+      </c>
+      <c r="H6" t="n">
+        <v>129.8598278169259</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B7" t="n">
+        <v>126.6821594238281</v>
+      </c>
+      <c r="C7" t="n">
+        <v>129</v>
+      </c>
+      <c r="D7" t="n">
+        <v>130.3999938964844</v>
+      </c>
+      <c r="E7" t="n">
+        <v>126.6999969482422</v>
+      </c>
+      <c r="F7" t="n">
+        <v>126.8000030517578</v>
+      </c>
+      <c r="G7" t="n">
+        <v>113773</v>
+      </c>
+      <c r="H7" t="n">
+        <v>129.7263393007843</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B8" t="n">
+        <v>128.1552124023438</v>
+      </c>
+      <c r="C8" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>131.1000061035156</v>
+      </c>
+      <c r="E8" t="n">
+        <v>129</v>
+      </c>
+      <c r="F8" t="n">
+        <v>129</v>
+      </c>
+      <c r="G8" t="n">
+        <v>84179</v>
+      </c>
+      <c r="H8" t="n">
+        <v>129.8060514039884</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B9" t="n">
+        <v>124.1288757324219</v>
+      </c>
+      <c r="C9" t="n">
+        <v>126.4000015258789</v>
+      </c>
+      <c r="D9" t="n">
+        <v>128.8999938964844</v>
+      </c>
+      <c r="E9" t="n">
+        <v>123.4000015258789</v>
+      </c>
+      <c r="F9" t="n">
+        <v>124.8000030517578</v>
+      </c>
+      <c r="G9" t="n">
+        <v>178461</v>
+      </c>
+      <c r="H9" t="n">
+        <v>129.1954419394737</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B10" t="n">
+        <v>112.6390914916992</v>
+      </c>
+      <c r="C10" t="n">
+        <v>114.6999969482422</v>
+      </c>
+      <c r="D10" t="n">
+        <v>118.5999984741211</v>
+      </c>
+      <c r="E10" t="n">
+        <v>112.3000030517578</v>
+      </c>
+      <c r="F10" t="n">
+        <v>116.1999969482422</v>
+      </c>
+      <c r="G10" t="n">
+        <v>509555</v>
+      </c>
+      <c r="H10" t="n">
+        <v>124.2877513520326</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B11" t="n">
+        <v>116.6654357910156</v>
+      </c>
+      <c r="C11" t="n">
+        <v>118.8000030517578</v>
+      </c>
+      <c r="D11" t="n">
+        <v>120.6999969482422</v>
+      </c>
+      <c r="E11" t="n">
+        <v>115</v>
+      </c>
+      <c r="F11" t="n">
+        <v>115.6999969482422</v>
+      </c>
+      <c r="G11" t="n">
+        <v>386472</v>
+      </c>
+      <c r="H11" t="n">
+        <v>123.1664943087692</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B12" t="n">
+        <v>117.6474685668945</v>
+      </c>
+      <c r="C12" t="n">
+        <v>119.8000030517578</v>
+      </c>
+      <c r="D12" t="n">
+        <v>121.4000015258789</v>
+      </c>
+      <c r="E12" t="n">
+        <v>119.0999984741211</v>
+      </c>
+      <c r="F12" t="n">
+        <v>120.5999984741211</v>
+      </c>
+      <c r="G12" t="n">
+        <v>263095</v>
+      </c>
+      <c r="H12" t="n">
+        <v>122.7554166890632</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B13" t="n">
+        <v>119.8079299926758</v>
+      </c>
+      <c r="C13" t="n">
+        <v>122</v>
+      </c>
+      <c r="D13" t="n">
+        <v>123.1999969482422</v>
+      </c>
+      <c r="E13" t="n">
+        <v>118</v>
+      </c>
+      <c r="F13" t="n">
+        <v>119.0999984741211</v>
+      </c>
+      <c r="G13" t="n">
+        <v>211583</v>
+      </c>
+      <c r="H13" t="n">
+        <v>122.6878676176599</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B14" t="n">
+        <v>118.5312881469727</v>
+      </c>
+      <c r="C14" t="n">
+        <v>120.6999969482422</v>
+      </c>
+      <c r="D14" t="n">
+        <v>120.9000015258789</v>
+      </c>
+      <c r="E14" t="n">
+        <v>117.0999984741211</v>
+      </c>
+      <c r="F14" t="n">
+        <v>120.6999969482422</v>
+      </c>
+      <c r="G14" t="n">
+        <v>193024</v>
+      </c>
+      <c r="H14" t="n">
+        <v>122.5379356082689</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B15" t="n">
+        <v>118.8258972167969</v>
+      </c>
+      <c r="C15" t="n">
+        <v>121</v>
+      </c>
+      <c r="D15" t="n">
+        <v>122</v>
+      </c>
+      <c r="E15" t="n">
+        <v>120</v>
+      </c>
+      <c r="F15" t="n">
+        <v>121.3000030517578</v>
+      </c>
+      <c r="G15" t="n">
+        <v>122910</v>
+      </c>
+      <c r="H15" t="n">
+        <v>122.4674585162678</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B16" t="n">
+        <v>120.0043334960938</v>
+      </c>
+      <c r="C16" t="n">
+        <v>122.1999969482422</v>
+      </c>
+      <c r="D16" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="E16" t="n">
+        <v>120.6999969482422</v>
+      </c>
+      <c r="F16" t="n">
+        <v>121.6999969482422</v>
+      </c>
+      <c r="G16" t="n">
+        <v>152554</v>
+      </c>
+      <c r="H16" t="n">
+        <v>122.4530644787105</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B17" t="n">
+        <v>117.8438720703125</v>
+      </c>
+      <c r="C17" t="n">
+        <v>120</v>
+      </c>
+      <c r="D17" t="n">
+        <v>122.3000030517578</v>
+      </c>
+      <c r="E17" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>122.0999984741211</v>
+      </c>
+      <c r="G17" t="n">
+        <v>166719</v>
+      </c>
+      <c r="H17" t="n">
+        <v>122.3168033699081</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B18" t="n">
+        <v>120.3971481323242</v>
+      </c>
+      <c r="C18" t="n">
+        <v>122.5999984741211</v>
+      </c>
+      <c r="D18" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="E18" t="n">
+        <v>119</v>
+      </c>
+      <c r="F18" t="n">
+        <v>121.1999969482422</v>
+      </c>
+      <c r="G18" t="n">
+        <v>160968</v>
+      </c>
+      <c r="H18" t="n">
+        <v>122.3312183660486</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B19" t="n">
+        <v>119.0223007202148</v>
+      </c>
+      <c r="C19" t="n">
+        <v>121.1999969482422</v>
+      </c>
+      <c r="D19" t="n">
+        <v>123.1999969482422</v>
+      </c>
+      <c r="E19" t="n">
+        <v>120.4000015258789</v>
+      </c>
+      <c r="F19" t="n">
+        <v>123.1999969482422</v>
+      </c>
+      <c r="G19" t="n">
+        <v>135399</v>
+      </c>
+      <c r="H19" t="n">
+        <v>122.2847727541856</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B20" t="n">
+        <v>118.9241027832031</v>
+      </c>
+      <c r="C20" t="n">
+        <v>121.0999984741211</v>
+      </c>
+      <c r="D20" t="n">
+        <v>124.1999969482422</v>
+      </c>
+      <c r="E20" t="n">
+        <v>121.0999984741211</v>
+      </c>
+      <c r="F20" t="n">
+        <v>122</v>
+      </c>
+      <c r="G20" t="n">
+        <v>171593</v>
+      </c>
+      <c r="H20" t="n">
+        <v>122.2261741434267</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B21" t="n">
+        <v>118.3348846435547</v>
+      </c>
+      <c r="C21" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>121.9000015258789</v>
+      </c>
+      <c r="E21" t="n">
+        <v>120.4000015258789</v>
+      </c>
+      <c r="F21" t="n">
+        <v>120.6999969482422</v>
+      </c>
+      <c r="G21" t="n">
+        <v>230831</v>
+      </c>
+      <c r="H21" t="n">
+        <v>122.1184889466561</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B22" t="n">
+        <v>119.6115264892578</v>
+      </c>
+      <c r="C22" t="n">
+        <v>121.8000030517578</v>
+      </c>
+      <c r="D22" t="n">
+        <v>122.5999984741211</v>
+      </c>
+      <c r="E22" t="n">
+        <v>119.1999969482422</v>
+      </c>
+      <c r="F22" t="n">
+        <v>120</v>
+      </c>
+      <c r="G22" t="n">
+        <v>160553</v>
+      </c>
+      <c r="H22" t="n">
+        <v>122.1052443428132</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B23" t="n">
+        <v>119.3169174194336</v>
+      </c>
+      <c r="C23" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="E23" t="n">
+        <v>120.0999984741211</v>
+      </c>
+      <c r="F23" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>150374</v>
+      </c>
+      <c r="H23" t="n">
+        <v>122.0825540891011</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B24" t="n">
+        <v>119.8079299926758</v>
+      </c>
+      <c r="C24" t="n">
+        <v>122</v>
+      </c>
+      <c r="D24" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="E24" t="n">
+        <v>121.8000030517578</v>
+      </c>
+      <c r="F24" t="n">
+        <v>122.0999984741211</v>
+      </c>
+      <c r="G24" t="n">
+        <v>196019</v>
+      </c>
+      <c r="H24" t="n">
+        <v>122.0787077165803</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,80 +1886,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>122.0752800594647</v>
+        <v>122.0787077165803</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125.3875453652953</v>
+        <v>122.0752800594647</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>127.2027482625323</v>
+        <v>125.3875453652953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>130.7767901530345</v>
+        <v>127.2027482625323</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>118.5205469791241</v>
+        <v>130.7767901530345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>136.7510754157676</v>
+        <v>118.5205469791241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>

--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -17,6 +17,7 @@
     <sheet name="2025-12" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2025-11" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="2025-10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2025-09" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,6 +141,23 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_202606" displayName="Table_202606" ref="A1:H23" headerRowCount="1">
+  <autoFilter ref="A1:H23"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table_202509" displayName="Table_202509" ref="A1:H23" headerRowCount="1">
   <autoFilter ref="A1:H23"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
@@ -1862,13 +1880,644 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B2" t="n">
+        <v>126.8785629272461</v>
+      </c>
+      <c r="C2" t="n">
+        <v>129.1999969482422</v>
+      </c>
+      <c r="D2" t="n">
+        <v>131</v>
+      </c>
+      <c r="E2" t="n">
+        <v>128</v>
+      </c>
+      <c r="F2" t="n">
+        <v>130</v>
+      </c>
+      <c r="G2" t="n">
+        <v>71485</v>
+      </c>
+      <c r="H2" t="n">
+        <v>129.1999969482422</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B3" t="n">
+        <v>125.209114074707</v>
+      </c>
+      <c r="C3" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E3" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="F3" t="n">
+        <v>129.3000030517578</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88068</v>
+      </c>
+      <c r="H3" t="n">
+        <v>128.261654634166</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B4" t="n">
+        <v>125.9947357177734</v>
+      </c>
+      <c r="C4" t="n">
+        <v>128.3000030517578</v>
+      </c>
+      <c r="D4" t="n">
+        <v>128.8000030517578</v>
+      </c>
+      <c r="E4" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="F4" t="n">
+        <v>128.3000030517578</v>
+      </c>
+      <c r="G4" t="n">
+        <v>59936</v>
+      </c>
+      <c r="H4" t="n">
+        <v>128.2721264608033</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B5" t="n">
+        <v>124.6198959350586</v>
+      </c>
+      <c r="C5" t="n">
+        <v>126.9000015258789</v>
+      </c>
+      <c r="D5" t="n">
+        <v>128.1999969482422</v>
+      </c>
+      <c r="E5" t="n">
+        <v>122.6999969482422</v>
+      </c>
+      <c r="F5" t="n">
+        <v>124</v>
+      </c>
+      <c r="G5" t="n">
+        <v>325602</v>
+      </c>
+      <c r="H5" t="n">
+        <v>127.4525080428488</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B6" t="n">
+        <v>123.0486450195312</v>
+      </c>
+      <c r="C6" t="n">
+        <v>125.3000030517578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>128.8000030517578</v>
+      </c>
+      <c r="E6" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="F6" t="n">
+        <v>127.8000030517578</v>
+      </c>
+      <c r="G6" t="n">
+        <v>143492</v>
+      </c>
+      <c r="H6" t="n">
+        <v>127.0039531900835</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B7" t="n">
+        <v>125.7983322143555</v>
+      </c>
+      <c r="C7" t="n">
+        <v>128.1000061035156</v>
+      </c>
+      <c r="D7" t="n">
+        <v>128.8999938964844</v>
+      </c>
+      <c r="E7" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="F7" t="n">
+        <v>126.4000015258789</v>
+      </c>
+      <c r="G7" t="n">
+        <v>153115</v>
+      </c>
+      <c r="H7" t="n">
+        <v>127.2033384111963</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B8" t="n">
+        <v>124.9144973754883</v>
+      </c>
+      <c r="C8" t="n">
+        <v>127.1999969482422</v>
+      </c>
+      <c r="D8" t="n">
+        <v>129.1999969482422</v>
+      </c>
+      <c r="E8" t="n">
+        <v>126.9000015258789</v>
+      </c>
+      <c r="F8" t="n">
+        <v>128.1000061035156</v>
+      </c>
+      <c r="G8" t="n">
+        <v>93934</v>
+      </c>
+      <c r="H8" t="n">
+        <v>127.2030029406468</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B9" t="n">
+        <v>128.7444305419922</v>
+      </c>
+      <c r="C9" t="n">
+        <v>131.1000061035156</v>
+      </c>
+      <c r="D9" t="n">
+        <v>132</v>
+      </c>
+      <c r="E9" t="n">
+        <v>126.4000015258789</v>
+      </c>
+      <c r="F9" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>110335</v>
+      </c>
+      <c r="H9" t="n">
+        <v>127.6140826821445</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B10" t="n">
+        <v>128.4498138427734</v>
+      </c>
+      <c r="C10" t="n">
+        <v>130.8000030517578</v>
+      </c>
+      <c r="D10" t="n">
+        <v>131.8999938964844</v>
+      </c>
+      <c r="E10" t="n">
+        <v>129.3999938964844</v>
+      </c>
+      <c r="F10" t="n">
+        <v>131.1999969482422</v>
+      </c>
+      <c r="G10" t="n">
+        <v>119536</v>
+      </c>
+      <c r="H10" t="n">
+        <v>127.9408361759597</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B11" t="n">
+        <v>131.2977142333984</v>
+      </c>
+      <c r="C11" t="n">
+        <v>133.6999969482422</v>
+      </c>
+      <c r="D11" t="n">
+        <v>134.3000030517578</v>
+      </c>
+      <c r="E11" t="n">
+        <v>131</v>
+      </c>
+      <c r="F11" t="n">
+        <v>132.3000030517578</v>
+      </c>
+      <c r="G11" t="n">
+        <v>86464</v>
+      </c>
+      <c r="H11" t="n">
+        <v>128.3385783504856</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B12" t="n">
+        <v>131.5923156738281</v>
+      </c>
+      <c r="C12" t="n">
+        <v>134</v>
+      </c>
+      <c r="D12" t="n">
+        <v>134.8000030517578</v>
+      </c>
+      <c r="E12" t="n">
+        <v>132.6999969482422</v>
+      </c>
+      <c r="F12" t="n">
+        <v>134.1000061035156</v>
+      </c>
+      <c r="G12" t="n">
+        <v>95923</v>
+      </c>
+      <c r="H12" t="n">
+        <v>128.7414751364892</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B13" t="n">
+        <v>131.4941101074219</v>
+      </c>
+      <c r="C13" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="D13" t="n">
+        <v>136.8000030517578</v>
+      </c>
+      <c r="E13" t="n">
+        <v>133.8000030517578</v>
+      </c>
+      <c r="F13" t="n">
+        <v>134</v>
+      </c>
+      <c r="G13" t="n">
+        <v>112126</v>
+      </c>
+      <c r="H13" t="n">
+        <v>129.1376379692823</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B14" t="n">
+        <v>127.4677886962891</v>
+      </c>
+      <c r="C14" t="n">
+        <v>129.8000030517578</v>
+      </c>
+      <c r="D14" t="n">
+        <v>134.3000030517578</v>
+      </c>
+      <c r="E14" t="n">
+        <v>129.3000030517578</v>
+      </c>
+      <c r="F14" t="n">
+        <v>134.1000061035156</v>
+      </c>
+      <c r="G14" t="n">
+        <v>122286</v>
+      </c>
+      <c r="H14" t="n">
+        <v>129.1888279295273</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B15" t="n">
+        <v>130.70849609375</v>
+      </c>
+      <c r="C15" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="D15" t="n">
+        <v>133.6000061035156</v>
+      </c>
+      <c r="E15" t="n">
+        <v>130.8999938964844</v>
+      </c>
+      <c r="F15" t="n">
+        <v>131.1000061035156</v>
+      </c>
+      <c r="G15" t="n">
+        <v>101444</v>
+      </c>
+      <c r="H15" t="n">
+        <v>129.4244724737056</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B16" t="n">
+        <v>131.2977142333984</v>
+      </c>
+      <c r="C16" t="n">
+        <v>133.6999969482422</v>
+      </c>
+      <c r="D16" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>132.3000030517578</v>
+      </c>
+      <c r="F16" t="n">
+        <v>133.6999969482422</v>
+      </c>
+      <c r="G16" t="n">
+        <v>147432</v>
+      </c>
+      <c r="H16" t="n">
+        <v>129.7687039598472</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B17" t="n">
+        <v>130.9049072265625</v>
+      </c>
+      <c r="C17" t="n">
+        <v>133.3000030517578</v>
+      </c>
+      <c r="D17" t="n">
+        <v>133.6999969482422</v>
+      </c>
+      <c r="E17" t="n">
+        <v>132.1000061035156</v>
+      </c>
+      <c r="F17" t="n">
+        <v>133.6999969482422</v>
+      </c>
+      <c r="G17" t="n">
+        <v>54545</v>
+      </c>
+      <c r="H17" t="n">
+        <v>129.8708476516664</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B18" t="n">
+        <v>132.1815490722656</v>
+      </c>
+      <c r="C18" t="n">
+        <v>134.6000061035156</v>
+      </c>
+      <c r="D18" t="n">
+        <v>136.8999938964844</v>
+      </c>
+      <c r="E18" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="F18" t="n">
+        <v>134</v>
+      </c>
+      <c r="G18" t="n">
+        <v>85036</v>
+      </c>
+      <c r="H18" t="n">
+        <v>130.0749054375811</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B19" t="n">
+        <v>132.5743560791016</v>
+      </c>
+      <c r="C19" t="n">
+        <v>135</v>
+      </c>
+      <c r="D19" t="n">
+        <v>135.1999969482422</v>
+      </c>
+      <c r="E19" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="F19" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>80029</v>
+      </c>
+      <c r="H19" t="n">
+        <v>130.2671000441108</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B20" t="n">
+        <v>128.6462249755859</v>
+      </c>
+      <c r="C20" t="n">
+        <v>131</v>
+      </c>
+      <c r="D20" t="n">
+        <v>135</v>
+      </c>
+      <c r="E20" t="n">
+        <v>129.8000030517578</v>
+      </c>
+      <c r="F20" t="n">
+        <v>134.8999938964844</v>
+      </c>
+      <c r="G20" t="n">
+        <v>119346</v>
+      </c>
+      <c r="H20" t="n">
+        <v>130.3074057017962</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B21" t="n">
+        <v>125.0127105712891</v>
+      </c>
+      <c r="C21" t="n">
+        <v>127.3000030517578</v>
+      </c>
+      <c r="D21" t="n">
+        <v>131.8000030517578</v>
+      </c>
+      <c r="E21" t="n">
+        <v>125.8000030517578</v>
+      </c>
+      <c r="F21" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>129461</v>
+      </c>
+      <c r="H21" t="n">
+        <v>130.1380970389766</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B22" t="n">
+        <v>126.6821594238281</v>
+      </c>
+      <c r="C22" t="n">
+        <v>129</v>
+      </c>
+      <c r="D22" t="n">
+        <v>130</v>
+      </c>
+      <c r="E22" t="n">
+        <v>128.1000061035156</v>
+      </c>
+      <c r="F22" t="n">
+        <v>129.6000061035156</v>
+      </c>
+      <c r="G22" t="n">
+        <v>109550</v>
+      </c>
+      <c r="H22" t="n">
+        <v>130.086344848627</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B23" t="n">
+        <v>123.7360610961914</v>
+      </c>
+      <c r="C23" t="n">
+        <v>126</v>
+      </c>
+      <c r="D23" t="n">
+        <v>128.3999938964844</v>
+      </c>
+      <c r="E23" t="n">
+        <v>124.8000030517578</v>
+      </c>
+      <c r="F23" t="n">
+        <v>128.1999969482422</v>
+      </c>
+      <c r="G23" t="n">
+        <v>208104</v>
+      </c>
+      <c r="H23" t="n">
+        <v>129.7614293712006</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1886,90 +2535,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>122.0787077165803</v>
+        <v>129.7614293712006</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>122.0752800594647</v>
+        <v>122.0787077165803</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>125.3875453652953</v>
+        <v>122.0752800594647</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>127.2027482625323</v>
+        <v>125.3875453652953</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130.7767901530345</v>
+        <v>127.2027482625323</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118.5205469791241</v>
+        <v>130.7767901530345</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>136.7510754157676</v>
+        <v>118.5205469791241</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>

--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -18,6 +18,7 @@
     <sheet name="2025-11" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="2025-10" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="2025-09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2025-08" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -159,6 +160,23 @@
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Table_202509" displayName="Table_202509" ref="A1:H23" headerRowCount="1">
   <autoFilter ref="A1:H23"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table_202508" displayName="Table_202508" ref="A1:H22" headerRowCount="1">
+  <autoFilter ref="A1:H22"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -2511,13 +2529,618 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B2" t="n">
+        <v>123.7360610961914</v>
+      </c>
+      <c r="C2" t="n">
+        <v>126</v>
+      </c>
+      <c r="D2" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>124.4000015258789</v>
+      </c>
+      <c r="F2" t="n">
+        <v>126.0999984741211</v>
+      </c>
+      <c r="G2" t="n">
+        <v>118056</v>
+      </c>
+      <c r="H2" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B3" t="n">
+        <v>125.209114074707</v>
+      </c>
+      <c r="C3" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>125.8000030517578</v>
+      </c>
+      <c r="F3" t="n">
+        <v>126.8000030517578</v>
+      </c>
+      <c r="G3" t="n">
+        <v>89209</v>
+      </c>
+      <c r="H3" t="n">
+        <v>126.6456155163679</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B4" t="n">
+        <v>123.9324645996094</v>
+      </c>
+      <c r="C4" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="D4" t="n">
+        <v>128.6000061035156</v>
+      </c>
+      <c r="E4" t="n">
+        <v>125.6999969482422</v>
+      </c>
+      <c r="F4" t="n">
+        <v>127.9000015258789</v>
+      </c>
+      <c r="G4" t="n">
+        <v>66318</v>
+      </c>
+      <c r="H4" t="n">
+        <v>126.5375951634916</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B5" t="n">
+        <v>125.5037231445312</v>
+      </c>
+      <c r="C5" t="n">
+        <v>127.8000030517578</v>
+      </c>
+      <c r="D5" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>125.6999969482422</v>
+      </c>
+      <c r="F5" t="n">
+        <v>127</v>
+      </c>
+      <c r="G5" t="n">
+        <v>105624</v>
+      </c>
+      <c r="H5" t="n">
+        <v>126.8892251987764</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B6" t="n">
+        <v>130.2174835205078</v>
+      </c>
+      <c r="C6" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="D6" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="E6" t="n">
+        <v>128.1000061035156</v>
+      </c>
+      <c r="F6" t="n">
+        <v>128.1000061035156</v>
+      </c>
+      <c r="G6" t="n">
+        <v>133317</v>
+      </c>
+      <c r="H6" t="n">
+        <v>128.3747052502025</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B7" t="n">
+        <v>132.770751953125</v>
+      </c>
+      <c r="C7" t="n">
+        <v>135.1999969482422</v>
+      </c>
+      <c r="D7" t="n">
+        <v>135.1999969482422</v>
+      </c>
+      <c r="E7" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="F7" t="n">
+        <v>133.3999938964844</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100235</v>
+      </c>
+      <c r="H7" t="n">
+        <v>129.4911851604984</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B8" t="n">
+        <v>132.5743560791016</v>
+      </c>
+      <c r="C8" t="n">
+        <v>135</v>
+      </c>
+      <c r="D8" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="F8" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65358</v>
+      </c>
+      <c r="H8" t="n">
+        <v>130.0221335370767</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B9" t="n">
+        <v>134.9312286376953</v>
+      </c>
+      <c r="C9" t="n">
+        <v>137.3999938964844</v>
+      </c>
+      <c r="D9" t="n">
+        <v>137.8000030517578</v>
+      </c>
+      <c r="E9" t="n">
+        <v>135.3000030517578</v>
+      </c>
+      <c r="F9" t="n">
+        <v>135.3999938964844</v>
+      </c>
+      <c r="G9" t="n">
+        <v>89963</v>
+      </c>
+      <c r="H9" t="n">
+        <v>130.8862810887815</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B10" t="n">
+        <v>131.5923156738281</v>
+      </c>
+      <c r="C10" t="n">
+        <v>134</v>
+      </c>
+      <c r="D10" t="n">
+        <v>138.6999969482422</v>
+      </c>
+      <c r="E10" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="F10" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>140577</v>
+      </c>
+      <c r="H10" t="n">
+        <v>131.3680000029398</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B11" t="n">
+        <v>135.8150634765625</v>
+      </c>
+      <c r="C11" t="n">
+        <v>138.3000030517578</v>
+      </c>
+      <c r="D11" t="n">
+        <v>138.3999938964844</v>
+      </c>
+      <c r="E11" t="n">
+        <v>135.1999969482422</v>
+      </c>
+      <c r="F11" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>119583</v>
+      </c>
+      <c r="H11" t="n">
+        <v>132.1741831125123</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B12" t="n">
+        <v>136.1096801757812</v>
+      </c>
+      <c r="C12" t="n">
+        <v>138.6000061035156</v>
+      </c>
+      <c r="D12" t="n">
+        <v>139.1000061035156</v>
+      </c>
+      <c r="E12" t="n">
+        <v>137.1000061035156</v>
+      </c>
+      <c r="F12" t="n">
+        <v>138.8999938964844</v>
+      </c>
+      <c r="G12" t="n">
+        <v>53383</v>
+      </c>
+      <c r="H12" t="n">
+        <v>132.4913266169762</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B13" t="n">
+        <v>136.3060760498047</v>
+      </c>
+      <c r="C13" t="n">
+        <v>138.8000030517578</v>
+      </c>
+      <c r="D13" t="n">
+        <v>139.3999938964844</v>
+      </c>
+      <c r="E13" t="n">
+        <v>137.3000030517578</v>
+      </c>
+      <c r="F13" t="n">
+        <v>138.3999938964844</v>
+      </c>
+      <c r="G13" t="n">
+        <v>75237</v>
+      </c>
+      <c r="H13" t="n">
+        <v>132.901614714865</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B14" t="n">
+        <v>138.466552734375</v>
+      </c>
+      <c r="C14" t="n">
+        <v>141</v>
+      </c>
+      <c r="D14" t="n">
+        <v>141.8999938964844</v>
+      </c>
+      <c r="E14" t="n">
+        <v>138.6999969482422</v>
+      </c>
+      <c r="F14" t="n">
+        <v>138.8999938964844</v>
+      </c>
+      <c r="G14" t="n">
+        <v>84686</v>
+      </c>
+      <c r="H14" t="n">
+        <v>133.4540065362368</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B15" t="n">
+        <v>132.6725616455078</v>
+      </c>
+      <c r="C15" t="n">
+        <v>135.1000061035156</v>
+      </c>
+      <c r="D15" t="n">
+        <v>140</v>
+      </c>
+      <c r="E15" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>140</v>
+      </c>
+      <c r="G15" t="n">
+        <v>129223</v>
+      </c>
+      <c r="H15" t="n">
+        <v>133.6091756435645</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B16" t="n">
+        <v>131.9851226806641</v>
+      </c>
+      <c r="C16" t="n">
+        <v>134.3999938964844</v>
+      </c>
+      <c r="D16" t="n">
+        <v>136</v>
+      </c>
+      <c r="E16" t="n">
+        <v>133.6000061035156</v>
+      </c>
+      <c r="F16" t="n">
+        <v>134.3999938964844</v>
+      </c>
+      <c r="G16" t="n">
+        <v>108379</v>
+      </c>
+      <c r="H16" t="n">
+        <v>133.6671198732381</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B17" t="n">
+        <v>134.5384216308594</v>
+      </c>
+      <c r="C17" t="n">
+        <v>137</v>
+      </c>
+      <c r="D17" t="n">
+        <v>137</v>
+      </c>
+      <c r="E17" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>134.1999969482422</v>
+      </c>
+      <c r="G17" t="n">
+        <v>88906</v>
+      </c>
+      <c r="H17" t="n">
+        <v>133.8560885188012</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B18" t="n">
+        <v>131.1995086669922</v>
+      </c>
+      <c r="C18" t="n">
+        <v>133.6000061035156</v>
+      </c>
+      <c r="D18" t="n">
+        <v>136.3999938964844</v>
+      </c>
+      <c r="E18" t="n">
+        <v>133.6000061035156</v>
+      </c>
+      <c r="F18" t="n">
+        <v>136.1999969482422</v>
+      </c>
+      <c r="G18" t="n">
+        <v>62187</v>
+      </c>
+      <c r="H18" t="n">
+        <v>133.8463200261923</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B19" t="n">
+        <v>127.664192199707</v>
+      </c>
+      <c r="C19" t="n">
+        <v>130</v>
+      </c>
+      <c r="D19" t="n">
+        <v>130.6999969482422</v>
+      </c>
+      <c r="E19" t="n">
+        <v>126.5999984741211</v>
+      </c>
+      <c r="F19" t="n">
+        <v>130</v>
+      </c>
+      <c r="G19" t="n">
+        <v>305699</v>
+      </c>
+      <c r="H19" t="n">
+        <v>133.2389581318738</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B20" t="n">
+        <v>127.4677886962891</v>
+      </c>
+      <c r="C20" t="n">
+        <v>129.8000030517578</v>
+      </c>
+      <c r="D20" t="n">
+        <v>130.8999938964844</v>
+      </c>
+      <c r="E20" t="n">
+        <v>128.6999969482422</v>
+      </c>
+      <c r="F20" t="n">
+        <v>130</v>
+      </c>
+      <c r="G20" t="n">
+        <v>112657</v>
+      </c>
+      <c r="H20" t="n">
+        <v>133.0498421844909</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B21" t="n">
+        <v>130.2174835205078</v>
+      </c>
+      <c r="C21" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="D21" t="n">
+        <v>133.3000030517578</v>
+      </c>
+      <c r="E21" t="n">
+        <v>130.3000030517578</v>
+      </c>
+      <c r="F21" t="n">
+        <v>130.6000061035156</v>
+      </c>
+      <c r="G21" t="n">
+        <v>86117</v>
+      </c>
+      <c r="H21" t="n">
+        <v>133.0316952412539</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B22" t="n">
+        <v>127.860595703125</v>
+      </c>
+      <c r="C22" t="n">
+        <v>130.1999969482422</v>
+      </c>
+      <c r="D22" t="n">
+        <v>132.8999938964844</v>
+      </c>
+      <c r="E22" t="n">
+        <v>130</v>
+      </c>
+      <c r="F22" t="n">
+        <v>132.3000030517578</v>
+      </c>
+      <c r="G22" t="n">
+        <v>87114</v>
+      </c>
+      <c r="H22" t="n">
+        <v>132.9206692909565</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2535,100 +3158,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>129.7614293712006</v>
+        <v>132.9206692909565</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>122.0787077165803</v>
+        <v>129.7614293712006</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>122.0752800594647</v>
+        <v>122.0787077165803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>125.3875453652953</v>
+        <v>122.0752800594647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>127.2027482625323</v>
+        <v>125.3875453652953</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>130.7767901530345</v>
+        <v>127.2027482625323</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>118.5205469791241</v>
+        <v>130.7767901530345</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136.7510754157676</v>
+        <v>118.5205469791241</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161.4922998677323</v>
+        <v>136.7510754157676</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>161.4922998677323</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>150.7558277000963</v>
       </c>
     </row>

--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -19,6 +19,7 @@
     <sheet name="2025-10" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="2025-09" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="2025-08" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-07" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -177,6 +178,23 @@
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Table_202508" displayName="Table_202508" ref="A1:H22" headerRowCount="1">
   <autoFilter ref="A1:H22"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table_202607" displayName="Table_202607" ref="A1:H24" headerRowCount="1">
+  <autoFilter ref="A1:H24"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -3134,13 +3152,670 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B2" t="n">
+        <v>140.1999969482422</v>
+      </c>
+      <c r="C2" t="n">
+        <v>140.1999969482422</v>
+      </c>
+      <c r="D2" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>138.6000061035156</v>
+      </c>
+      <c r="F2" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>141080</v>
+      </c>
+      <c r="H2" t="n">
+        <v>140.1999969482422</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B3" t="n">
+        <v>138.3000030517578</v>
+      </c>
+      <c r="C3" t="n">
+        <v>138.3000030517578</v>
+      </c>
+      <c r="D3" t="n">
+        <v>142.3000030517578</v>
+      </c>
+      <c r="E3" t="n">
+        <v>135</v>
+      </c>
+      <c r="F3" t="n">
+        <v>138.1999969482422</v>
+      </c>
+      <c r="G3" t="n">
+        <v>245709</v>
+      </c>
+      <c r="H3" t="n">
+        <v>138.9930194997851</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B4" t="n">
+        <v>142</v>
+      </c>
+      <c r="C4" t="n">
+        <v>142</v>
+      </c>
+      <c r="D4" t="n">
+        <v>142</v>
+      </c>
+      <c r="E4" t="n">
+        <v>139.3999938964844</v>
+      </c>
+      <c r="F4" t="n">
+        <v>140.1000061035156</v>
+      </c>
+      <c r="G4" t="n">
+        <v>123663</v>
+      </c>
+      <c r="H4" t="n">
+        <v>139.7214958885505</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B5" t="n">
+        <v>141.1999969482422</v>
+      </c>
+      <c r="C5" t="n">
+        <v>141.1999969482422</v>
+      </c>
+      <c r="D5" t="n">
+        <v>141.3000030517578</v>
+      </c>
+      <c r="E5" t="n">
+        <v>136.6000061035156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>141.3000030517578</v>
+      </c>
+      <c r="G5" t="n">
+        <v>161666</v>
+      </c>
+      <c r="H5" t="n">
+        <v>140.0771229545063</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B6" t="n">
+        <v>134.3000030517578</v>
+      </c>
+      <c r="C6" t="n">
+        <v>134.3000030517578</v>
+      </c>
+      <c r="D6" t="n">
+        <v>139.3000030517578</v>
+      </c>
+      <c r="E6" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="F6" t="n">
+        <v>139.3000030517578</v>
+      </c>
+      <c r="G6" t="n">
+        <v>162778</v>
+      </c>
+      <c r="H6" t="n">
+        <v>138.9507694643356</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B7" t="n">
+        <v>130.8000030517578</v>
+      </c>
+      <c r="C7" t="n">
+        <v>130.8000030517578</v>
+      </c>
+      <c r="D7" t="n">
+        <v>135</v>
+      </c>
+      <c r="E7" t="n">
+        <v>130.1000061035156</v>
+      </c>
+      <c r="F7" t="n">
+        <v>134.6000061035156</v>
+      </c>
+      <c r="G7" t="n">
+        <v>168496</v>
+      </c>
+      <c r="H7" t="n">
+        <v>137.5820406550031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B8" t="n">
+        <v>132.8000030517578</v>
+      </c>
+      <c r="C8" t="n">
+        <v>132.8000030517578</v>
+      </c>
+      <c r="D8" t="n">
+        <v>134.1999969482422</v>
+      </c>
+      <c r="E8" t="n">
+        <v>131.8999938964844</v>
+      </c>
+      <c r="F8" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="G8" t="n">
+        <v>153121</v>
+      </c>
+      <c r="H8" t="n">
+        <v>136.9489043393313</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B9" t="n">
+        <v>134</v>
+      </c>
+      <c r="C9" t="n">
+        <v>134</v>
+      </c>
+      <c r="D9" t="n">
+        <v>134.1999969482422</v>
+      </c>
+      <c r="E9" t="n">
+        <v>132.3999938964844</v>
+      </c>
+      <c r="F9" t="n">
+        <v>132.3999938964844</v>
+      </c>
+      <c r="G9" t="n">
+        <v>145970</v>
+      </c>
+      <c r="H9" t="n">
+        <v>136.6184189768259</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B10" t="n">
+        <v>133.8000030517578</v>
+      </c>
+      <c r="C10" t="n">
+        <v>133.8000030517578</v>
+      </c>
+      <c r="D10" t="n">
+        <v>133.8000030517578</v>
+      </c>
+      <c r="E10" t="n">
+        <v>131.1000061035156</v>
+      </c>
+      <c r="F10" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="G10" t="n">
+        <v>111023</v>
+      </c>
+      <c r="H10" t="n">
+        <v>136.3970481504913</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B11" t="n">
+        <v>135.8000030517578</v>
+      </c>
+      <c r="C11" t="n">
+        <v>135.8000030517578</v>
+      </c>
+      <c r="D11" t="n">
+        <v>138.6999969482422</v>
+      </c>
+      <c r="E11" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="G11" t="n">
+        <v>122132</v>
+      </c>
+      <c r="H11" t="n">
+        <v>136.3495641002148</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B12" t="n">
+        <v>136</v>
+      </c>
+      <c r="C12" t="n">
+        <v>136</v>
+      </c>
+      <c r="D12" t="n">
+        <v>137.1999969482422</v>
+      </c>
+      <c r="E12" t="n">
+        <v>134.1999969482422</v>
+      </c>
+      <c r="F12" t="n">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="G12" t="n">
+        <v>183299</v>
+      </c>
+      <c r="H12" t="n">
+        <v>136.3122883012732</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B13" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="C13" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="D13" t="n">
+        <v>136.3999938964844</v>
+      </c>
+      <c r="E13" t="n">
+        <v>130.8999938964844</v>
+      </c>
+      <c r="F13" t="n">
+        <v>136.1000061035156</v>
+      </c>
+      <c r="G13" t="n">
+        <v>230850</v>
+      </c>
+      <c r="H13" t="n">
+        <v>136.026678558596</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B14" t="n">
+        <v>135.3000030517578</v>
+      </c>
+      <c r="C14" t="n">
+        <v>135.3000030517578</v>
+      </c>
+      <c r="D14" t="n">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="E14" t="n">
+        <v>130.8000030517578</v>
+      </c>
+      <c r="F14" t="n">
+        <v>131.8999938964844</v>
+      </c>
+      <c r="G14" t="n">
+        <v>228124</v>
+      </c>
+      <c r="H14" t="n">
+        <v>135.9505633622808</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B15" t="n">
+        <v>133.3999938964844</v>
+      </c>
+      <c r="C15" t="n">
+        <v>133.3999938964844</v>
+      </c>
+      <c r="D15" t="n">
+        <v>137.1000061035156</v>
+      </c>
+      <c r="E15" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="F15" t="n">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="G15" t="n">
+        <v>151157</v>
+      </c>
+      <c r="H15" t="n">
+        <v>135.7850308708545</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B16" t="n">
+        <v>134.8000030517578</v>
+      </c>
+      <c r="C16" t="n">
+        <v>134.8000030517578</v>
+      </c>
+      <c r="D16" t="n">
+        <v>135.6999969482422</v>
+      </c>
+      <c r="E16" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="F16" t="n">
+        <v>134.1000061035156</v>
+      </c>
+      <c r="G16" t="n">
+        <v>116522</v>
+      </c>
+      <c r="H16" t="n">
+        <v>135.7380984694557</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B17" t="n">
+        <v>134.1000061035156</v>
+      </c>
+      <c r="C17" t="n">
+        <v>134.1000061035156</v>
+      </c>
+      <c r="D17" t="n">
+        <v>134.8999938964844</v>
+      </c>
+      <c r="E17" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="F17" t="n">
+        <v>134.1999969482422</v>
+      </c>
+      <c r="G17" t="n">
+        <v>128326</v>
+      </c>
+      <c r="H17" t="n">
+        <v>135.6564291993818</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B18" t="n">
+        <v>133.8000030517578</v>
+      </c>
+      <c r="C18" t="n">
+        <v>133.8000030517578</v>
+      </c>
+      <c r="D18" t="n">
+        <v>134.8999938964844</v>
+      </c>
+      <c r="E18" t="n">
+        <v>132.3999938964844</v>
+      </c>
+      <c r="F18" t="n">
+        <v>134.1000061035156</v>
+      </c>
+      <c r="G18" t="n">
+        <v>133262</v>
+      </c>
+      <c r="H18" t="n">
+        <v>135.5650458247811</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B19" t="n">
+        <v>132.1999969482422</v>
+      </c>
+      <c r="C19" t="n">
+        <v>132.1999969482422</v>
+      </c>
+      <c r="D19" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="E19" t="n">
+        <v>131.6999969482422</v>
+      </c>
+      <c r="F19" t="n">
+        <v>133</v>
+      </c>
+      <c r="G19" t="n">
+        <v>111709</v>
+      </c>
+      <c r="H19" t="n">
+        <v>135.4316931061552</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B20" t="n">
+        <v>130.3000030517578</v>
+      </c>
+      <c r="C20" t="n">
+        <v>130.3000030517578</v>
+      </c>
+      <c r="D20" t="n">
+        <v>132.8000030517578</v>
+      </c>
+      <c r="E20" t="n">
+        <v>128.6000061035156</v>
+      </c>
+      <c r="F20" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>182544</v>
+      </c>
+      <c r="H20" t="n">
+        <v>135.1195889034299</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B21" t="n">
+        <v>124.0999984741211</v>
+      </c>
+      <c r="C21" t="n">
+        <v>124.0999984741211</v>
+      </c>
+      <c r="D21" t="n">
+        <v>131</v>
+      </c>
+      <c r="E21" t="n">
+        <v>123.8000030517578</v>
+      </c>
+      <c r="F21" t="n">
+        <v>130</v>
+      </c>
+      <c r="G21" t="n">
+        <v>219376</v>
+      </c>
+      <c r="H21" t="n">
+        <v>134.3690212134007</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B22" t="n">
+        <v>128.6000061035156</v>
+      </c>
+      <c r="C22" t="n">
+        <v>128.6000061035156</v>
+      </c>
+      <c r="D22" t="n">
+        <v>134.3000030517578</v>
+      </c>
+      <c r="E22" t="n">
+        <v>126.9000015258789</v>
+      </c>
+      <c r="F22" t="n">
+        <v>130</v>
+      </c>
+      <c r="G22" t="n">
+        <v>356962</v>
+      </c>
+      <c r="H22" t="n">
+        <v>133.7934336973663</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B23" t="n">
+        <v>131.6000061035156</v>
+      </c>
+      <c r="C23" t="n">
+        <v>131.6000061035156</v>
+      </c>
+      <c r="D23" t="n">
+        <v>131.6000061035156</v>
+      </c>
+      <c r="E23" t="n">
+        <v>125.1999969482422</v>
+      </c>
+      <c r="F23" t="n">
+        <v>129</v>
+      </c>
+      <c r="G23" t="n">
+        <v>281040</v>
+      </c>
+      <c r="H23" t="n">
+        <v>133.6336846942475</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B24" t="n">
+        <v>131.8000030517578</v>
+      </c>
+      <c r="C24" t="n">
+        <v>131.8000030517578</v>
+      </c>
+      <c r="D24" t="n">
+        <v>136.1999969482422</v>
+      </c>
+      <c r="E24" t="n">
+        <v>131.8000030517578</v>
+      </c>
+      <c r="F24" t="n">
+        <v>133.3999938964844</v>
+      </c>
+      <c r="G24" t="n">
+        <v>329359</v>
+      </c>
+      <c r="H24" t="n">
+        <v>133.4894833269459</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3263,6 +3938,16 @@
       </c>
       <c r="B12" t="n">
         <v>150.7558277000963</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>133.4894833269459</v>
       </c>
     </row>
   </sheetData>

--- a/Nexans_VWAP.xlsx
+++ b/Nexans_VWAP.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026-06" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="VWAP_Mensuel" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2026-05" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2026-04" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2026-03" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2026-02" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2026-01" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2025-12" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2025-11" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2025-10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="2025-09" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="2025-08" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="2026-07" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-06" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VWAP_Mensuel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-05" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-04" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-01" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-12" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-11" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-08" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-07" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-08" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -195,6 +196,23 @@
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table_202607" displayName="Table_202607" ref="A1:H24" headerRowCount="1">
   <autoFilter ref="A1:H24"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Adj Close"/>
+    <tableColumn id="3" name="Close"/>
+    <tableColumn id="4" name="High"/>
+    <tableColumn id="5" name="Low"/>
+    <tableColumn id="6" name="Open"/>
+    <tableColumn id="7" name="Volume"/>
+    <tableColumn id="8" name="VWAP"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Table_202608" displayName="Table_202608" ref="A1:H22" headerRowCount="1">
+  <autoFilter ref="A1:H22"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Adj Close"/>
@@ -3809,13 +3827,618 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adj Close</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="n">
+        <v>129.1999969482422</v>
+      </c>
+      <c r="C2" t="n">
+        <v>129.1999969482422</v>
+      </c>
+      <c r="D2" t="n">
+        <v>133.3000030517578</v>
+      </c>
+      <c r="E2" t="n">
+        <v>127.3000030517578</v>
+      </c>
+      <c r="F2" t="n">
+        <v>132.8999938964844</v>
+      </c>
+      <c r="G2" t="n">
+        <v>290202</v>
+      </c>
+      <c r="H2" t="n">
+        <v>129.1999969482422</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B3" t="n">
+        <v>132.8999938964844</v>
+      </c>
+      <c r="C3" t="n">
+        <v>132.8999938964844</v>
+      </c>
+      <c r="D3" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="E3" t="n">
+        <v>129.6000061035156</v>
+      </c>
+      <c r="F3" t="n">
+        <v>129.8999938964844</v>
+      </c>
+      <c r="G3" t="n">
+        <v>231852</v>
+      </c>
+      <c r="H3" t="n">
+        <v>130.8432210063738</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B4" t="n">
+        <v>138.1000061035156</v>
+      </c>
+      <c r="C4" t="n">
+        <v>138.1000061035156</v>
+      </c>
+      <c r="D4" t="n">
+        <v>142.6999969482422</v>
+      </c>
+      <c r="E4" t="n">
+        <v>136.1000061035156</v>
+      </c>
+      <c r="F4" t="n">
+        <v>142</v>
+      </c>
+      <c r="G4" t="n">
+        <v>393468</v>
+      </c>
+      <c r="H4" t="n">
+        <v>133.9620021155139</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B5" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>142.1000061035156</v>
+      </c>
+      <c r="E5" t="n">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>137.8999938964844</v>
+      </c>
+      <c r="G5" t="n">
+        <v>261557</v>
+      </c>
+      <c r="H5" t="n">
+        <v>135.4148010463185</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B6" t="n">
+        <v>139.6000061035156</v>
+      </c>
+      <c r="C6" t="n">
+        <v>139.6000061035156</v>
+      </c>
+      <c r="D6" t="n">
+        <v>141.8000030517578</v>
+      </c>
+      <c r="E6" t="n">
+        <v>138.8000030517578</v>
+      </c>
+      <c r="F6" t="n">
+        <v>140.3000030517578</v>
+      </c>
+      <c r="G6" t="n">
+        <v>207524</v>
+      </c>
+      <c r="H6" t="n">
+        <v>136.0420786806222</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B7" t="n">
+        <v>137.8999938964844</v>
+      </c>
+      <c r="C7" t="n">
+        <v>137.8999938964844</v>
+      </c>
+      <c r="D7" t="n">
+        <v>141.1999969482422</v>
+      </c>
+      <c r="E7" t="n">
+        <v>137.6999969482422</v>
+      </c>
+      <c r="F7" t="n">
+        <v>139.8999938964844</v>
+      </c>
+      <c r="G7" t="n">
+        <v>160048</v>
+      </c>
+      <c r="H7" t="n">
+        <v>136.2345853468324</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B8" t="n">
+        <v>138.8000030517578</v>
+      </c>
+      <c r="C8" t="n">
+        <v>138.8000030517578</v>
+      </c>
+      <c r="D8" t="n">
+        <v>140.8000030517578</v>
+      </c>
+      <c r="E8" t="n">
+        <v>137.6000061035156</v>
+      </c>
+      <c r="F8" t="n">
+        <v>138</v>
+      </c>
+      <c r="G8" t="n">
+        <v>146227</v>
+      </c>
+      <c r="H8" t="n">
+        <v>136.4564424735667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B9" t="n">
+        <v>144.6999969482422</v>
+      </c>
+      <c r="C9" t="n">
+        <v>144.6999969482422</v>
+      </c>
+      <c r="D9" t="n">
+        <v>144.6999969482422</v>
+      </c>
+      <c r="E9" t="n">
+        <v>139.3999938964844</v>
+      </c>
+      <c r="F9" t="n">
+        <v>139.3999938964844</v>
+      </c>
+      <c r="G9" t="n">
+        <v>168545</v>
+      </c>
+      <c r="H9" t="n">
+        <v>137.2036688383767</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B10" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>145.1999969482422</v>
+      </c>
+      <c r="E10" t="n">
+        <v>142.1999969482422</v>
+      </c>
+      <c r="F10" t="n">
+        <v>145.1999969482422</v>
+      </c>
+      <c r="G10" t="n">
+        <v>175359</v>
+      </c>
+      <c r="H10" t="n">
+        <v>137.6601105290203</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B11" t="n">
+        <v>140</v>
+      </c>
+      <c r="C11" t="n">
+        <v>140</v>
+      </c>
+      <c r="D11" t="n">
+        <v>143.3000030517578</v>
+      </c>
+      <c r="E11" t="n">
+        <v>139.8000030517578</v>
+      </c>
+      <c r="F11" t="n">
+        <v>142.8999938964844</v>
+      </c>
+      <c r="G11" t="n">
+        <v>140962</v>
+      </c>
+      <c r="H11" t="n">
+        <v>137.8117071780784</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B12" t="n">
+        <v>140.8999938964844</v>
+      </c>
+      <c r="C12" t="n">
+        <v>140.8999938964844</v>
+      </c>
+      <c r="D12" t="n">
+        <v>142.1999969482422</v>
+      </c>
+      <c r="E12" t="n">
+        <v>140.6999969482422</v>
+      </c>
+      <c r="F12" t="n">
+        <v>140.8000030517578</v>
+      </c>
+      <c r="G12" t="n">
+        <v>92871</v>
+      </c>
+      <c r="H12" t="n">
+        <v>137.9381333349296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B13" t="n">
+        <v>138</v>
+      </c>
+      <c r="C13" t="n">
+        <v>138</v>
+      </c>
+      <c r="D13" t="n">
+        <v>140.3000030517578</v>
+      </c>
+      <c r="E13" t="n">
+        <v>137.3999938964844</v>
+      </c>
+      <c r="F13" t="n">
+        <v>140</v>
+      </c>
+      <c r="G13" t="n">
+        <v>138880</v>
+      </c>
+      <c r="H13" t="n">
+        <v>137.9417022073239</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B14" t="n">
+        <v>138.1000061035156</v>
+      </c>
+      <c r="C14" t="n">
+        <v>138.1000061035156</v>
+      </c>
+      <c r="D14" t="n">
+        <v>139.8000030517578</v>
+      </c>
+      <c r="E14" t="n">
+        <v>136.8000030517578</v>
+      </c>
+      <c r="F14" t="n">
+        <v>137.6999969482422</v>
+      </c>
+      <c r="G14" t="n">
+        <v>119794</v>
+      </c>
+      <c r="H14" t="n">
+        <v>137.94920584341</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B15" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>139.1999969482422</v>
+      </c>
+      <c r="E15" t="n">
+        <v>136.3000030517578</v>
+      </c>
+      <c r="F15" t="n">
+        <v>138.3000030517578</v>
+      </c>
+      <c r="G15" t="n">
+        <v>148035</v>
+      </c>
+      <c r="H15" t="n">
+        <v>137.9796832035245</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B16" t="n">
+        <v>141.8000030517578</v>
+      </c>
+      <c r="C16" t="n">
+        <v>141.8000030517578</v>
+      </c>
+      <c r="D16" t="n">
+        <v>143.6000061035156</v>
+      </c>
+      <c r="E16" t="n">
+        <v>137.8999938964844</v>
+      </c>
+      <c r="F16" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>158024</v>
+      </c>
+      <c r="H16" t="n">
+        <v>138.1927534736421</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B17" t="n">
+        <v>137.3000030517578</v>
+      </c>
+      <c r="C17" t="n">
+        <v>137.3000030517578</v>
+      </c>
+      <c r="D17" t="n">
+        <v>141.6999969482422</v>
+      </c>
+      <c r="E17" t="n">
+        <v>136.6999969482422</v>
+      </c>
+      <c r="F17" t="n">
+        <v>141.1000061035156</v>
+      </c>
+      <c r="G17" t="n">
+        <v>162282</v>
+      </c>
+      <c r="H17" t="n">
+        <v>138.144390583711</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B18" t="n">
+        <v>140.8000030517578</v>
+      </c>
+      <c r="C18" t="n">
+        <v>140.8000030517578</v>
+      </c>
+      <c r="D18" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>137.6999969482422</v>
+      </c>
+      <c r="F18" t="n">
+        <v>137.6999969482422</v>
+      </c>
+      <c r="G18" t="n">
+        <v>98720</v>
+      </c>
+      <c r="H18" t="n">
+        <v>138.2291134052553</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B19" t="n">
+        <v>141</v>
+      </c>
+      <c r="C19" t="n">
+        <v>141</v>
+      </c>
+      <c r="D19" t="n">
+        <v>142.3999938964844</v>
+      </c>
+      <c r="E19" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>141.1999969482422</v>
+      </c>
+      <c r="G19" t="n">
+        <v>96918</v>
+      </c>
+      <c r="H19" t="n">
+        <v>138.3132645285673</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B20" t="n">
+        <v>142.6999969482422</v>
+      </c>
+      <c r="C20" t="n">
+        <v>142.6999969482422</v>
+      </c>
+      <c r="D20" t="n">
+        <v>145.8000030517578</v>
+      </c>
+      <c r="E20" t="n">
+        <v>141.6000061035156</v>
+      </c>
+      <c r="F20" t="n">
+        <v>141.6999969482422</v>
+      </c>
+      <c r="G20" t="n">
+        <v>140460</v>
+      </c>
+      <c r="H20" t="n">
+        <v>138.4982017250213</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B21" t="n">
+        <v>142.6000061035156</v>
+      </c>
+      <c r="C21" t="n">
+        <v>142.6000061035156</v>
+      </c>
+      <c r="D21" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>142.3999938964844</v>
+      </c>
+      <c r="F21" t="n">
+        <v>143</v>
+      </c>
+      <c r="G21" t="n">
+        <v>116874</v>
+      </c>
+      <c r="H21" t="n">
+        <v>138.6372129199728</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B22" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>142.6000061035156</v>
+      </c>
+      <c r="E22" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>142.6000061035156</v>
+      </c>
+      <c r="G22" t="n">
+        <v>153677</v>
+      </c>
+      <c r="H22" t="n">
+        <v>138.6740203216475</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3948,6 +4571,16 @@
       </c>
       <c r="B13" t="n">
         <v>133.4894833269459</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>138.6740203216475</v>
       </c>
     </row>
   </sheetData>
